--- a/db/A7XLK-1101-House.xlsx
+++ b/db/A7XLK-1101-House.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou2/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB0AFBB-37BB-DE4F-92CB-7DDDC44E593B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3078EEF-0C95-9444-AA39-A4CC7D50374D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2860" yWindow="840" windowWidth="35940" windowHeight="18200" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="-3700" yWindow="-21100" windowWidth="36360" windowHeight="13780" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="1072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="1095">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4090,6 +4090,98 @@
   </si>
   <si>
     <t xml:space="preserve">	10757 坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>單價2022</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>34~36 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>29萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27~29 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>44~49 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>35~37 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26~28萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27~28 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>38~42 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>35~40 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>38~43 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>33~36 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>26~28 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>28萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>34~39 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>32~34 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>38~41 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>45~48 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>24~25 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30~32 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>29.8~38.2 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>35~42 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>45~50 萬/坪</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4524,35 +4616,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89EF37-C3F3-8243-B091-96A26EC57E26}">
-  <dimension ref="A1:AP50"/>
+  <dimension ref="A1:AQ50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
     <col min="2" max="2" width="14.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="28.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="60.33203125" style="2" customWidth="1"/>
-    <col min="5" max="8" width="15.83203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" style="2" customWidth="1"/>
-    <col min="10" max="11" width="8.83203125" style="2"/>
-    <col min="12" max="12" width="19.83203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" style="2"/>
-    <col min="14" max="14" width="39" style="2" customWidth="1"/>
-    <col min="15" max="19" width="8.83203125" style="2"/>
-    <col min="20" max="20" width="22.6640625" style="2" customWidth="1"/>
-    <col min="21" max="22" width="10.5" style="2" customWidth="1"/>
-    <col min="23" max="25" width="8.83203125" style="2"/>
-    <col min="26" max="26" width="29.1640625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="8.83203125" style="2"/>
-    <col min="28" max="28" width="31" style="2" customWidth="1"/>
-    <col min="29" max="29" width="17" style="2" customWidth="1"/>
-    <col min="30" max="30" width="8.83203125" style="2"/>
-    <col min="31" max="31" width="8.83203125" style="1"/>
-    <col min="32" max="34" width="8.83203125" style="2"/>
-    <col min="35" max="35" width="11.6640625" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="8.83203125" style="2"/>
+    <col min="5" max="9" width="15.83203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" style="2" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" style="2"/>
+    <col min="13" max="13" width="19.83203125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="2"/>
+    <col min="15" max="15" width="39" style="2" customWidth="1"/>
+    <col min="16" max="20" width="8.83203125" style="2"/>
+    <col min="21" max="21" width="22.6640625" style="2" customWidth="1"/>
+    <col min="22" max="23" width="10.5" style="2" customWidth="1"/>
+    <col min="24" max="26" width="8.83203125" style="2"/>
+    <col min="27" max="27" width="29.1640625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="8.83203125" style="2"/>
+    <col min="29" max="29" width="31" style="2" customWidth="1"/>
+    <col min="30" max="30" width="17" style="2" customWidth="1"/>
+    <col min="31" max="31" width="8.83203125" style="2"/>
+    <col min="32" max="32" width="8.83203125" style="1"/>
+    <col min="33" max="35" width="8.83203125" style="2"/>
+    <col min="36" max="36" width="11.6640625" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4569,118 +4661,121 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>938</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>1002</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>1000</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>1003</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:43">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -4696,107 +4791,110 @@
       <c r="E2" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="8">
+      <c r="K2" s="8">
         <v>0.8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="Y2" s="8">
+      <c r="Z2" s="8">
         <v>0.33</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="AA2" s="7">
+      <c r="AB2" s="7">
         <v>0.40899999999999997</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ2" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM2" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="AN2" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP2" s="2" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:43">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -4812,110 +4910,113 @@
       <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="S3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="T3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="W3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="X3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" s="2" t="s">
+      <c r="AB3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AF3" s="2" t="s">
+      <c r="AG3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG3" s="2" t="s">
+      <c r="AH3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AH3" s="2" t="s">
+      <c r="AI3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI3" s="2" t="s">
+      <c r="AJ3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ3" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK3" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AN3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN3" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP3" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP3" s="2" t="s">
+      <c r="AQ3" s="2" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:43">
       <c r="A4" s="1" t="s">
         <v>69</v>
       </c>
@@ -4932,115 +5033,118 @@
         <v>41</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>973</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Z4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="AA4" s="2" t="s">
+      <c r="AB4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AB4" s="2" t="s">
+      <c r="AC4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC4" s="2" t="s">
+      <c r="AD4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AD4" s="2" t="s">
+      <c r="AE4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE4" s="1">
+      <c r="AF4" s="1">
         <v>4.2361111111111099E-2</v>
       </c>
-      <c r="AF4" s="2" t="s">
+      <c r="AG4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG4" s="2" t="s">
+      <c r="AH4" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AH4" s="2" t="s">
+      <c r="AI4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI4" s="2" t="s">
+      <c r="AJ4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ4" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK4" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="AM4" s="2" t="s">
+      <c r="AN4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="AN4" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP4" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="AP4" s="2" t="s">
+      <c r="AQ4" s="2" t="s">
         <v>1049</v>
       </c>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:43">
       <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
@@ -5057,115 +5161,118 @@
         <v>93</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>971</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="S5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Y5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AA5" s="2" t="s">
+      <c r="AB5" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AB5" s="2" t="s">
+      <c r="AC5" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AC5" s="2" t="s">
+      <c r="AD5" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AD5" s="2" t="s">
+      <c r="AE5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AE5" s="1" t="s">
+      <c r="AF5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AF5" s="2" t="s">
+      <c r="AG5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG5" s="2" t="s">
+      <c r="AH5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AH5" s="2" t="s">
+      <c r="AI5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI5" s="2" t="s">
+      <c r="AJ5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ5" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK5" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AN5" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AN5" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP5" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="AP5" s="2" t="s">
+      <c r="AQ5" s="2" t="s">
         <v>1051</v>
       </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:43">
       <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
@@ -5181,110 +5288,113 @@
       <c r="E6" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="J6" s="8">
+      <c r="K6" s="8">
         <v>0.8</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Z6" s="7">
         <v>0.32600000000000001</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AB6" s="7">
         <v>0.44269999999999998</v>
       </c>
-      <c r="AB6" s="2" t="s">
+      <c r="AC6" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="AC6" s="7" t="s">
+      <c r="AD6" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AE6" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="AE6" s="1" t="s">
+      <c r="AF6" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="AF6" s="2" t="s">
+      <c r="AG6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG6" s="2" t="s">
+      <c r="AH6" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="AH6" s="2" t="s">
+      <c r="AI6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI6" s="2" t="s">
+      <c r="AJ6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ6" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK6" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM6" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="AM6" s="2" t="s">
+      <c r="AN6" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="AN6" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP6" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="AP6" s="2" t="s">
+      <c r="AQ6" s="2" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="7" spans="1:42">
+    <row r="7" spans="1:43">
       <c r="A7" s="1" t="s">
         <v>113</v>
       </c>
@@ -5300,110 +5410,113 @@
       <c r="E7" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AD7" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="AD7" s="2" t="s">
+      <c r="AE7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE7" s="1" t="s">
+      <c r="AF7" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AG7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG7" s="2" t="s">
+      <c r="AH7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="AH7" s="2" t="s">
+      <c r="AI7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AJ7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ7" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK7" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM7" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AN7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN7" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP7" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="AP7" s="2" t="s">
+      <c r="AQ7" s="2" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="8" spans="1:42">
+    <row r="8" spans="1:43">
       <c r="A8" s="1" t="s">
         <v>134</v>
       </c>
@@ -5420,115 +5533,118 @@
         <v>138</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>969</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>968</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AA8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="AB8" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AC8" s="2" t="s">
+      <c r="AD8" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="AD8" s="2" t="s">
+      <c r="AE8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE8" s="1">
+      <c r="AF8" s="1">
         <v>4.2361111111111099E-2</v>
       </c>
-      <c r="AF8" s="2" t="s">
+      <c r="AG8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG8" s="2" t="s">
+      <c r="AH8" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="AH8" s="2" t="s">
+      <c r="AI8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI8" s="2" t="s">
+      <c r="AJ8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK8" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM8" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="AM8" s="2" t="s">
+      <c r="AN8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP8" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP8" s="2" t="s">
+      <c r="AQ8" s="2" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="9" spans="1:42">
+    <row r="9" spans="1:43">
       <c r="A9" s="1" t="s">
         <v>153</v>
       </c>
@@ -5544,110 +5660,113 @@
       <c r="E9" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="U9" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="X9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Z9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="AA9" s="2" t="s">
+      <c r="AB9" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="AB9" s="2" t="s">
+      <c r="AC9" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AC9" s="2" t="s">
+      <c r="AD9" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="AD9" s="2" t="s">
+      <c r="AE9" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="AE9" s="1" t="s">
+      <c r="AF9" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AF9" s="2" t="s">
+      <c r="AG9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG9" s="2" t="s">
+      <c r="AH9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="AH9" s="2" t="s">
+      <c r="AI9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI9" s="2" t="s">
+      <c r="AJ9" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AJ9" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AM9" s="2" t="s">
+      <c r="AN9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AN9" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP9" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP9" s="2" t="s">
+      <c r="AQ9" s="2" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="10" spans="1:42">
+    <row r="10" spans="1:43">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -5663,110 +5782,113 @@
       <c r="E10" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="U10" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="U10" s="3" t="s">
+      <c r="V10" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="X10" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Z10" s="2" t="s">
+      <c r="AA10" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="AA10" s="2" t="s">
+      <c r="AB10" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="AB10" s="2" t="s">
+      <c r="AC10" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="AC10" s="2" t="s">
+      <c r="AD10" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="AD10" s="2" t="s">
+      <c r="AE10" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="AE10" s="1" t="s">
+      <c r="AF10" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AF10" s="2" t="s">
+      <c r="AG10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG10" s="2" t="s">
+      <c r="AH10" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="AH10" s="2" t="s">
+      <c r="AI10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI10" s="2" t="s">
+      <c r="AJ10" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="AJ10" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK10" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM10" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="AM10" s="2" t="s">
+      <c r="AN10" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="AN10" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP10" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP10" s="2" t="s">
+      <c r="AQ10" s="2" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="11" spans="1:42">
+    <row r="11" spans="1:43">
       <c r="A11" s="1" t="s">
         <v>203</v>
       </c>
@@ -5782,110 +5904,113 @@
       <c r="E11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="U11" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="X11" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Z11" s="2" t="s">
+      <c r="AA11" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="AA11" s="2" t="s">
+      <c r="AB11" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="AB11" s="2" t="s">
+      <c r="AC11" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AC11" s="2" t="s">
+      <c r="AD11" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="AD11" s="2" t="s">
+      <c r="AE11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE11" s="1" t="s">
+      <c r="AF11" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AF11" s="2" t="s">
+      <c r="AG11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG11" s="2" t="s">
+      <c r="AH11" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="AH11" s="2" t="s">
+      <c r="AI11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI11" s="2" t="s">
+      <c r="AJ11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ11" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK11" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM11" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="AM11" s="2" t="s">
+      <c r="AN11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN11" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP11" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP11" s="2" t="s">
+      <c r="AQ11" s="2" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="16">
+    <row r="12" spans="1:43" ht="16">
       <c r="A12" s="1" t="s">
         <v>219</v>
       </c>
@@ -5902,112 +6027,115 @@
         <v>581</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="J12" s="8">
+      <c r="K12" s="8">
         <v>0.8</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="M12" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="O12" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="P12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="U12" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="Y12" s="7">
+      <c r="Z12" s="7">
         <v>0.31859999999999999</v>
       </c>
-      <c r="Z12" s="2" t="s">
+      <c r="AA12" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AB12" s="7">
         <v>0.47989999999999999</v>
       </c>
-      <c r="AB12" s="2" t="s">
+      <c r="AC12" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC12" s="7" t="s">
+      <c r="AD12" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="AD12" s="2" t="s">
+      <c r="AE12" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="AE12" s="1" t="s">
+      <c r="AF12" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF12" s="2" t="s">
+      <c r="AG12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG12" s="2" t="s">
+      <c r="AH12" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="AH12" s="2" t="s">
+      <c r="AI12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI12" s="2" t="s">
+      <c r="AJ12" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ12" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK12" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM12" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="AM12" s="2" t="s">
+      <c r="AN12" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="AN12" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP12" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP12" s="2" t="s">
+      <c r="AQ12" s="2" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="13" spans="1:42">
+    <row r="13" spans="1:43">
       <c r="A13" s="1" t="s">
         <v>772</v>
       </c>
@@ -6024,115 +6152,118 @@
         <v>225</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>964</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="U13" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="V13" s="2" t="s">
+      <c r="W13" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="X13" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="X13" s="2" t="s">
+      <c r="Y13" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="Y13" s="2" t="s">
+      <c r="Z13" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="Z13" s="2" t="s">
+      <c r="AA13" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="AA13" s="2" t="s">
+      <c r="AB13" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="AB13" s="2" t="s">
+      <c r="AC13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AC13" s="2" t="s">
+      <c r="AD13" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="AD13" s="2" t="s">
+      <c r="AE13" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="AE13" s="1" t="s">
+      <c r="AF13" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AF13" s="2" t="s">
+      <c r="AG13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG13" s="2" t="s">
+      <c r="AH13" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="AH13" s="2" t="s">
+      <c r="AI13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI13" s="2" t="s">
+      <c r="AJ13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AJ13" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK13" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM13" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="AM13" s="2" t="s">
+      <c r="AN13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AN13" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP13" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP13" s="9" t="s">
+      <c r="AQ13" s="9" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="14" spans="1:42" ht="16">
+    <row r="14" spans="1:43" ht="16">
       <c r="A14" s="1" t="s">
         <v>773</v>
       </c>
@@ -6148,110 +6279,113 @@
       <c r="E14" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="U14" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="V14" s="2" t="s">
+      <c r="W14" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="X14" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="X14" s="2" t="s">
+      <c r="Y14" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="Y14" s="2" t="s">
+      <c r="Z14" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="Z14" s="2" t="s">
+      <c r="AA14" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="AA14" s="2" t="s">
+      <c r="AB14" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="AB14" s="2" t="s">
+      <c r="AC14" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="AC14" s="2" t="s">
+      <c r="AD14" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="AD14" s="2" t="s">
+      <c r="AE14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE14" s="1" t="s">
+      <c r="AF14" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AF14" s="2" t="s">
+      <c r="AG14" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG14" s="2" t="s">
+      <c r="AH14" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="AH14" s="2" t="s">
+      <c r="AI14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI14" s="2" t="s">
+      <c r="AJ14" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ14" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK14" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM14" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="AM14" s="2" t="s">
+      <c r="AN14" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="AN14" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP14" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP14" s="2" t="s">
+      <c r="AQ14" s="2" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="15" spans="1:42" ht="16">
+    <row r="15" spans="1:43" ht="16">
       <c r="A15" s="1" t="s">
         <v>786</v>
       </c>
@@ -6267,107 +6401,110 @@
       <c r="E15" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="M15" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="U15" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="V15" s="2" t="s">
+      <c r="W15" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="X15" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="X15" s="2" t="s">
+      <c r="Y15" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="Y15" s="2" t="s">
+      <c r="Z15" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="Z15" s="2" t="s">
+      <c r="AA15" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AB15" s="7">
         <v>0.4743</v>
       </c>
-      <c r="AB15" s="2" t="s">
+      <c r="AC15" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC15" s="2" t="s">
+      <c r="AD15" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="AD15" s="2" t="s">
+      <c r="AE15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE15" s="1" t="s">
+      <c r="AF15" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AF15" s="2" t="s">
+      <c r="AG15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG15" s="2" t="s">
+      <c r="AH15" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="AH15" s="2" t="s">
+      <c r="AI15" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI15" s="2" t="s">
+      <c r="AJ15" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AK15" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AL15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM15" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="AM15" s="2" t="s">
+      <c r="AN15" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="AN15" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP15" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP15" s="2" t="s">
+      <c r="AQ15" s="2" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="16" spans="1:42">
+    <row r="16" spans="1:43">
       <c r="A16" s="1" t="s">
         <v>776</v>
       </c>
@@ -6383,110 +6520,113 @@
       <c r="E16" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="2" t="s">
+      <c r="M16" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="P16" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="U16" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="V16" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="V16" s="2" t="s">
+      <c r="W16" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="X16" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="X16" s="2" t="s">
+      <c r="Y16" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="Y16" s="7">
+      <c r="Z16" s="7">
         <v>0.33800000000000002</v>
       </c>
-      <c r="Z16" s="2" t="s">
+      <c r="AA16" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AB16" s="7">
         <v>0.45529999999999998</v>
       </c>
-      <c r="AB16" s="2" t="s">
+      <c r="AC16" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="AC16" s="7" t="s">
+      <c r="AD16" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="AD16" s="2" t="s">
+      <c r="AE16" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="AE16" s="1" t="s">
+      <c r="AF16" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AF16" s="2" t="s">
+      <c r="AG16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG16" s="2" t="s">
+      <c r="AH16" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="AH16" s="2" t="s">
+      <c r="AI16" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI16" s="2" t="s">
+      <c r="AJ16" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="AJ16" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK16" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM16" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="AM16" s="2" t="s">
+      <c r="AN16" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="AN16" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP16" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP16" s="2" t="s">
+      <c r="AQ16" s="2" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="17" spans="1:42">
+    <row r="17" spans="1:43">
       <c r="A17" s="1" t="s">
         <v>264</v>
       </c>
@@ -6502,110 +6642,113 @@
       <c r="E17" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="2" t="s">
+      <c r="M17" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="O17" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="U17" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="U17" s="3" t="s">
+      <c r="V17" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="V17" s="2" t="s">
+      <c r="W17" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="X17" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="X17" s="2" t="s">
+      <c r="Y17" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="Y17" s="2" t="s">
+      <c r="Z17" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Z17" s="2" t="s">
+      <c r="AA17" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AA17" s="2" t="s">
+      <c r="AB17" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="AB17" s="2" t="s">
+      <c r="AC17" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="AC17" s="2" t="s">
+      <c r="AD17" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="AD17" s="2" t="s">
+      <c r="AE17" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE17" s="1" t="s">
+      <c r="AF17" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="AF17" s="2" t="s">
+      <c r="AG17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG17" s="2" t="s">
+      <c r="AH17" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="AH17" s="2" t="s">
+      <c r="AI17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI17" s="2" t="s">
+      <c r="AJ17" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ17" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK17" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM17" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AM17" s="2" t="s">
+      <c r="AN17" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AN17" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP17" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP17" s="9" t="s">
+      <c r="AQ17" s="9" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="18" spans="1:42">
+    <row r="18" spans="1:43">
       <c r="A18" s="1" t="s">
         <v>777</v>
       </c>
@@ -6621,110 +6764,113 @@
       <c r="E18" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="M18" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="O18" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="U18" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="V18" s="2" t="s">
+      <c r="W18" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="X18" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="X18" s="2" t="s">
+      <c r="Y18" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="Y18" s="2" t="s">
+      <c r="Z18" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="Z18" s="2" t="s">
+      <c r="AA18" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="AA18" s="2" t="s">
+      <c r="AB18" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="AB18" s="2" t="s">
+      <c r="AC18" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="AC18" s="2" t="s">
+      <c r="AD18" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="AD18" s="2" t="s">
+      <c r="AE18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE18" s="1" t="s">
+      <c r="AF18" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AF18" s="2" t="s">
+      <c r="AG18" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG18" s="2" t="s">
+      <c r="AH18" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="AH18" s="2" t="s">
+      <c r="AI18" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI18" s="2" t="s">
+      <c r="AJ18" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ18" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK18" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM18" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="AM18" s="2" t="s">
+      <c r="AN18" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="AN18" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP18" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP18" s="2" t="s">
+      <c r="AQ18" s="2" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="19" spans="1:42">
+    <row r="19" spans="1:43">
       <c r="A19" s="1" t="s">
         <v>778</v>
       </c>
@@ -6741,115 +6887,118 @@
         <v>751</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>963</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>962</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="O19" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="S19" s="2" t="s">
         <v>755</v>
       </c>
       <c r="T19" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="V19" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="V19" s="2" t="s">
+      <c r="W19" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="X19" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="X19" s="2" t="s">
+      <c r="Y19" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="Y19" s="7">
+      <c r="Z19" s="7">
         <v>0.33500000000000002</v>
       </c>
-      <c r="Z19" s="2" t="s">
+      <c r="AA19" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="AA19" s="7">
+      <c r="AB19" s="7">
         <v>0.59850000000000003</v>
       </c>
-      <c r="AB19" s="2" t="s">
+      <c r="AC19" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC19" s="7" t="s">
+      <c r="AD19" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="AD19" s="2" t="s">
+      <c r="AE19" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="AE19" s="1" t="s">
+      <c r="AF19" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="AF19" s="2" t="s">
+      <c r="AG19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG19" s="2" t="s">
+      <c r="AH19" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="AH19" s="2" t="s">
+      <c r="AI19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI19" s="2" t="s">
+      <c r="AJ19" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AJ19" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK19" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM19" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="AM19" s="2" t="s">
+      <c r="AN19" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="AN19" s="2" t="s">
+      <c r="AO19" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="AO19" s="2" t="s">
+      <c r="AP19" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP19" s="2" t="s">
+      <c r="AQ19" s="2" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="20" spans="1:42">
+    <row r="20" spans="1:43">
       <c r="A20" s="1" t="s">
         <v>779</v>
       </c>
@@ -6866,115 +7015,118 @@
         <v>350</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="H20" s="9" t="s">
         <v>960</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="M20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="U20" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="V20" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="V20" s="2" t="s">
+      <c r="W20" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="X20" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="X20" s="2" t="s">
+      <c r="Y20" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Y20" s="2" t="s">
+      <c r="Z20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z20" s="2" t="s">
+      <c r="AA20" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="AA20" s="2" t="s">
+      <c r="AB20" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="AB20" s="2" t="s">
+      <c r="AC20" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AC20" s="2" t="s">
+      <c r="AD20" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="AD20" s="2" t="s">
+      <c r="AE20" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE20" s="1">
+      <c r="AF20" s="1">
         <v>4.2361111111111099E-2</v>
       </c>
-      <c r="AF20" s="2" t="s">
+      <c r="AG20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG20" s="2" t="s">
+      <c r="AH20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AH20" s="2" t="s">
+      <c r="AI20" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI20" s="2" t="s">
+      <c r="AJ20" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AJ20" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK20" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM20" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="AM20" s="2" t="s">
+      <c r="AN20" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN20" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP20" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP20" s="2" t="s">
+      <c r="AQ20" s="2" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="21" spans="1:42">
+    <row r="21" spans="1:43">
       <c r="A21" s="1" t="s">
         <v>326</v>
       </c>
@@ -6990,110 +7142,113 @@
       <c r="E21" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="J21" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="2" t="s">
+      <c r="M21" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="P21" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="S21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="T21" s="2" t="s">
+      <c r="U21" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="V21" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="V21" s="2" t="s">
+      <c r="W21" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="W21" s="2" t="s">
+      <c r="X21" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="X21" s="2" t="s">
+      <c r="Y21" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="Y21" s="8">
+      <c r="Z21" s="8">
         <v>0.34</v>
       </c>
-      <c r="Z21" s="2" t="s">
+      <c r="AA21" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="AA21" s="7">
+      <c r="AB21" s="7">
         <v>0.44359999999999999</v>
       </c>
-      <c r="AB21" s="2" t="s">
+      <c r="AC21" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="AC21" s="2" t="s">
+      <c r="AD21" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="AD21" s="2" t="s">
+      <c r="AE21" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE21" s="1" t="s">
+      <c r="AF21" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="AF21" s="2" t="s">
+      <c r="AG21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG21" s="2" t="s">
+      <c r="AH21" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="AH21" s="2" t="s">
+      <c r="AI21" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI21" s="2" t="s">
+      <c r="AJ21" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ21" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK21" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM21" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="AM21" s="2" t="s">
+      <c r="AN21" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="AN21" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP21" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP21" s="2" t="s">
+      <c r="AQ21" s="2" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="22" spans="1:42">
+    <row r="22" spans="1:43">
       <c r="A22" s="1" t="s">
         <v>343</v>
       </c>
@@ -7109,110 +7264,113 @@
       <c r="E22" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="K22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="L22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="O22" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="U22" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="V22" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="V22" s="2" t="s">
+      <c r="W22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="W22" s="2" t="s">
+      <c r="X22" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="X22" s="2" t="s">
+      <c r="Y22" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="Y22" s="2" t="s">
+      <c r="Z22" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="Z22" s="2" t="s">
+      <c r="AA22" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="AA22" s="2" t="s">
+      <c r="AB22" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AB22" s="2" t="s">
+      <c r="AC22" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AC22" s="2" t="s">
+      <c r="AD22" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="AD22" s="2" t="s">
+      <c r="AE22" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AE22" s="1" t="s">
+      <c r="AF22" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="AF22" s="2" t="s">
+      <c r="AG22" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG22" s="2" t="s">
+      <c r="AH22" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="AH22" s="2" t="s">
+      <c r="AI22" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI22" s="2" t="s">
+      <c r="AJ22" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AJ22" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK22" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM22" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="AM22" s="2" t="s">
+      <c r="AN22" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="AN22" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP22" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="AP22" s="9" t="s">
+      <c r="AQ22" s="9" t="s">
         <v>1057</v>
       </c>
     </row>
-    <row r="23" spans="1:42">
+    <row r="23" spans="1:43">
       <c r="A23" s="1" t="s">
         <v>346</v>
       </c>
@@ -7228,110 +7386,113 @@
       <c r="E23" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J23" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="L23" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="O23" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="S23" s="2" t="s">
         <v>388</v>
       </c>
       <c r="T23" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="U23" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="V23" s="2" t="s">
+      <c r="W23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="X23" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="X23" s="2" t="s">
+      <c r="Y23" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Y23" s="2" t="s">
+      <c r="Z23" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="Z23" s="2" t="s">
+      <c r="AA23" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="AA23" s="2" t="s">
+      <c r="AB23" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="AB23" s="2" t="s">
+      <c r="AC23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="AC23" s="2" t="s">
+      <c r="AD23" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AD23" s="2" t="s">
+      <c r="AE23" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE23" s="1" t="s">
+      <c r="AF23" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AF23" s="2" t="s">
+      <c r="AG23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG23" s="2" t="s">
+      <c r="AH23" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AH23" s="2" t="s">
+      <c r="AI23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI23" s="2" t="s">
+      <c r="AJ23" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AJ23" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK23" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM23" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="AM23" s="2" t="s">
+      <c r="AN23" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AN23" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP23" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="AP23" s="2" t="s">
+      <c r="AQ23" s="2" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="24" spans="1:42">
+    <row r="24" spans="1:43">
       <c r="A24" s="1" t="s">
         <v>362</v>
       </c>
@@ -7348,115 +7509,118 @@
         <v>620</v>
       </c>
       <c r="F24" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="H24" s="9" t="s">
         <v>957</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="L24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R24" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="S24" s="2" t="s">
+      <c r="T24" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="U24" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="V24" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="V24" s="2" t="s">
+      <c r="W24" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="X24" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="X24" s="2" t="s">
+      <c r="Y24" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="Y24" s="8">
+      <c r="Z24" s="8">
         <v>0.32</v>
       </c>
-      <c r="Z24" s="2" t="s">
+      <c r="AA24" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="AA24" s="7">
+      <c r="AB24" s="7">
         <v>0.44209999999999999</v>
       </c>
-      <c r="AB24" s="2" t="s">
+      <c r="AC24" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC24" s="2" t="s">
+      <c r="AD24" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="AD24" s="2" t="s">
+      <c r="AE24" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="AE24" s="1" t="s">
+      <c r="AF24" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF24" s="2" t="s">
+      <c r="AG24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG24" s="2" t="s">
+      <c r="AH24" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="AH24" s="2" t="s">
+      <c r="AI24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI24" s="2" t="s">
+      <c r="AJ24" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK24" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM24" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="AM24" s="2" t="s">
+      <c r="AN24" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="AN24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP24" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="AP24" s="2" t="s">
+      <c r="AQ24" s="2" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="25" spans="1:42">
+    <row r="25" spans="1:43">
       <c r="A25" s="1" t="s">
         <v>788</v>
       </c>
@@ -7472,107 +7636,110 @@
       <c r="E25" s="2" t="s">
         <v>815</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J25" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="L25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="T25" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="T25" s="2" t="s">
+      <c r="U25" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="U25" s="2" t="s">
+      <c r="V25" s="2" t="s">
         <v>821</v>
       </c>
-      <c r="V25" s="2" t="s">
+      <c r="W25" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W25" s="2" t="s">
+      <c r="X25" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="X25" s="2" t="s">
+      <c r="Y25" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="Y25" s="8">
+      <c r="Z25" s="8">
         <v>0.32</v>
       </c>
-      <c r="Z25" s="2" t="s">
+      <c r="AA25" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="AA25" s="7">
+      <c r="AB25" s="7">
         <v>0.55610000000000004</v>
       </c>
-      <c r="AB25" s="2" t="s">
+      <c r="AC25" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="AC25" s="2" t="s">
+      <c r="AD25" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="AD25" s="2" t="s">
+      <c r="AE25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE25" s="1" t="s">
+      <c r="AF25" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF25" s="2" t="s">
+      <c r="AG25" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG25" s="2" t="s">
+      <c r="AH25" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="AH25" s="2" t="s">
+      <c r="AI25" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI25" s="2" t="s">
+      <c r="AJ25" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AK25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AL25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM25" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="AM25" s="2" t="s">
+      <c r="AN25" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="AN25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP25" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP25" s="2" t="s">
+      <c r="AQ25" s="2" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="26" spans="1:42">
+    <row r="26" spans="1:43">
       <c r="A26" s="1" t="s">
         <v>790</v>
       </c>
@@ -7588,107 +7755,110 @@
       <c r="E26" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="O26" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R26" s="2" t="s">
+      <c r="S26" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="S26" s="2" t="s">
+      <c r="T26" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="T26" s="2" t="s">
+      <c r="U26" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="U26" s="2" t="s">
+      <c r="V26" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="V26" s="2" t="s">
+      <c r="W26" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W26" s="2" t="s">
+      <c r="X26" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="X26" s="2" t="s">
+      <c r="Y26" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="Y26" s="8">
+      <c r="Z26" s="8">
         <v>0.32500000000000001</v>
       </c>
-      <c r="Z26" s="2" t="s">
+      <c r="AA26" s="2" t="s">
         <v>809</v>
       </c>
-      <c r="AA26" s="7">
+      <c r="AB26" s="7">
         <v>0.3347</v>
       </c>
-      <c r="AB26" s="2" t="s">
+      <c r="AC26" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="AC26" s="2" t="s">
+      <c r="AD26" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="AD26" s="2" t="s">
+      <c r="AE26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE26" s="1" t="s">
+      <c r="AF26" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF26" s="2" t="s">
+      <c r="AG26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG26" s="2" t="s">
+      <c r="AH26" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="AH26" s="2" t="s">
+      <c r="AI26" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI26" s="2" t="s">
+      <c r="AJ26" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AK26" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AL26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM26" s="2" t="s">
         <v>812</v>
       </c>
-      <c r="AM26" s="2" t="s">
+      <c r="AN26" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="AN26" s="2" t="s">
+      <c r="AO26" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="AO26" s="2" t="s">
+      <c r="AP26" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="AP26" s="2" t="s">
+      <c r="AQ26" s="2" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="27" spans="1:42">
+    <row r="27" spans="1:43">
       <c r="A27" s="1" t="s">
         <v>774</v>
       </c>
@@ -7705,112 +7875,115 @@
         <v>116</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>955</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="L27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R27" s="2" t="s">
+      <c r="S27" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="S27" s="2" t="s">
+      <c r="T27" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="T27" s="2" t="s">
+      <c r="U27" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="V27" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="V27" s="2" t="s">
+      <c r="W27" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="W27" s="2" t="s">
+      <c r="X27" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="X27" s="2" t="s">
+      <c r="Y27" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="Y27" s="2" t="s">
+      <c r="Z27" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="Z27" s="2" t="s">
+      <c r="AA27" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="AA27" s="2" t="s">
+      <c r="AB27" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="AB27" s="2" t="s">
+      <c r="AC27" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AC27" s="2" t="s">
+      <c r="AD27" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="AD27" s="2" t="s">
+      <c r="AE27" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE27" s="1" t="s">
+      <c r="AF27" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="AF27" s="2" t="s">
+      <c r="AG27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG27" s="2" t="s">
+      <c r="AH27" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="AH27" s="2" t="s">
+      <c r="AI27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI27" s="2" t="s">
+      <c r="AJ27" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ27" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK27" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM27" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="AM27" s="2" t="s">
+      <c r="AN27" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="AN27" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO27" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP27" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP27" s="2" t="s">
+      <c r="AQ27" s="2" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="28" spans="1:42">
+    <row r="28" spans="1:43">
       <c r="A28" s="1" t="s">
         <v>775</v>
       </c>
@@ -7827,115 +8000,118 @@
         <v>330</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>954</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="H28" s="9" t="s">
         <v>953</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="O28" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="S28" s="2" t="s">
         <v>333</v>
       </c>
       <c r="T28" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="U28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="V28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="V28" s="2" t="s">
+      <c r="W28" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W28" s="2" t="s">
+      <c r="X28" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="X28" s="2" t="s">
+      <c r="Y28" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Y28" s="2" t="s">
+      <c r="Z28" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="Z28" s="2" t="s">
+      <c r="AA28" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="AA28" s="2" t="s">
+      <c r="AB28" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="AB28" s="2" t="s">
+      <c r="AC28" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="AC28" s="2" t="s">
+      <c r="AD28" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="AD28" s="2" t="s">
+      <c r="AE28" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE28" s="1" t="s">
+      <c r="AF28" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="AF28" s="2" t="s">
+      <c r="AG28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG28" s="2" t="s">
+      <c r="AH28" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="AH28" s="2" t="s">
+      <c r="AI28" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI28" s="2" t="s">
+      <c r="AJ28" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ28" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK28" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM28" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="AM28" s="2" t="s">
+      <c r="AN28" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="AN28" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO28" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP28" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP28" s="2" t="s">
+      <c r="AQ28" s="2" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="29" spans="1:42">
+    <row r="29" spans="1:43">
       <c r="A29" s="1" t="s">
         <v>780</v>
       </c>
@@ -7951,110 +8127,113 @@
       <c r="E29" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J29" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="L29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L29" s="5" t="s">
+      <c r="M29" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R29" s="2" t="s">
+      <c r="S29" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="T29" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="T29" s="2" t="s">
+      <c r="U29" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="V29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="V29" s="2" t="s">
+      <c r="W29" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W29" s="2" t="s">
+      <c r="X29" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="X29" s="2" t="s">
+      <c r="Y29" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="Y29" s="2" t="s">
+      <c r="Z29" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z29" s="2" t="s">
+      <c r="AA29" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AA29" s="2" t="s">
+      <c r="AB29" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="AB29" s="2" t="s">
+      <c r="AC29" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="AC29" s="2" t="s">
+      <c r="AD29" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="AD29" s="2" t="s">
+      <c r="AE29" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE29" s="1" t="s">
+      <c r="AF29" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="AF29" s="2" t="s">
+      <c r="AG29" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG29" s="2" t="s">
+      <c r="AH29" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="AH29" s="2" t="s">
+      <c r="AI29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI29" s="2" t="s">
+      <c r="AJ29" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ29" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK29" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM29" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="AM29" s="2" t="s">
+      <c r="AN29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN29" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP29" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP29" s="2" t="s">
+      <c r="AQ29" s="2" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="30" spans="1:42">
+    <row r="30" spans="1:43">
       <c r="A30" s="1" t="s">
         <v>439</v>
       </c>
@@ -8070,110 +8249,113 @@
       <c r="E30" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L30" s="5" t="s">
+      <c r="M30" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="S30" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="T30" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="T30" s="2" t="s">
+      <c r="U30" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="V30" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="V30" s="2" t="s">
+      <c r="W30" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="W30" s="2" t="s">
+      <c r="X30" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="X30" s="2" t="s">
+      <c r="Y30" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="Y30" s="2" t="s">
+      <c r="Z30" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="Z30" s="2" t="s">
+      <c r="AA30" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="AA30" s="2" t="s">
+      <c r="AB30" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="AB30" s="2" t="s">
+      <c r="AC30" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="AC30" s="2" t="s">
+      <c r="AD30" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="AD30" s="2" t="s">
+      <c r="AE30" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE30" s="1" t="s">
+      <c r="AF30" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AF30" s="2" t="s">
+      <c r="AG30" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG30" s="2" t="s">
+      <c r="AH30" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="AH30" s="2" t="s">
+      <c r="AI30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI30" s="2" t="s">
+      <c r="AJ30" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="AJ30" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK30" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM30" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="AM30" s="2" t="s">
+      <c r="AN30" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="AN30" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP30" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP30" s="2" t="s">
+      <c r="AQ30" s="2" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="31" spans="1:42">
+    <row r="31" spans="1:43">
       <c r="A31" s="1" t="s">
         <v>457</v>
       </c>
@@ -8189,110 +8371,113 @@
       <c r="E31" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="L31" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L31" s="2" t="s">
+      <c r="M31" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R31" s="2" t="s">
+      <c r="S31" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="S31" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="T31" s="2" t="s">
+      <c r="U31" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="V31" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="V31" s="2" t="s">
+      <c r="W31" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W31" s="2" t="s">
+      <c r="X31" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="X31" s="2" t="s">
+      <c r="Y31" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="Y31" s="8">
+      <c r="Z31" s="8">
         <v>0.32</v>
       </c>
-      <c r="Z31" s="2" t="s">
+      <c r="AA31" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="AA31" s="7">
+      <c r="AB31" s="7">
         <v>0.46450000000000002</v>
       </c>
-      <c r="AB31" s="2" t="s">
+      <c r="AC31" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC31" s="2" t="s">
+      <c r="AD31" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="AD31" s="2" t="s">
+      <c r="AE31" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE31" s="1" t="s">
+      <c r="AF31" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF31" s="2" t="s">
+      <c r="AG31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG31" s="2" t="s">
+      <c r="AH31" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="AH31" s="2" t="s">
+      <c r="AI31" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI31" s="2" t="s">
+      <c r="AJ31" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ31" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM31" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="AM31" s="2" t="s">
+      <c r="AN31" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="AN31" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP31" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP31" s="2" t="s">
+      <c r="AQ31" s="2" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="32" spans="1:42">
+    <row r="32" spans="1:43">
       <c r="A32" s="1" t="s">
         <v>460</v>
       </c>
@@ -8309,115 +8494,118 @@
         <v>243</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="H32" s="9" t="s">
         <v>951</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="O32" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P32" s="2" t="s">
+      <c r="Q32" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="R32" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R32" s="2" t="s">
+      <c r="S32" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="S32" s="2" t="s">
+      <c r="T32" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="T32" s="2" t="s">
+      <c r="U32" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="V32" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="V32" s="2" t="s">
+      <c r="W32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W32" s="2" t="s">
+      <c r="X32" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="X32" s="2" t="s">
+      <c r="Y32" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="Y32" s="2" t="s">
+      <c r="Z32" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Z32" s="2" t="s">
+      <c r="AA32" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="AA32" s="2" t="s">
+      <c r="AB32" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="AB32" s="2" t="s">
+      <c r="AC32" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="AC32" s="2" t="s">
+      <c r="AD32" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="AD32" s="2" t="s">
+      <c r="AE32" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE32" s="1" t="s">
+      <c r="AF32" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="AF32" s="2" t="s">
+      <c r="AG32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG32" s="2" t="s">
+      <c r="AH32" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="AH32" s="2" t="s">
+      <c r="AI32" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI32" s="2" t="s">
+      <c r="AJ32" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="AJ32" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK32" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM32" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="AM32" s="2" t="s">
+      <c r="AN32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN32" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP32" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP32" s="9" t="s">
+      <c r="AQ32" s="9" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="33" spans="1:42">
+    <row r="33" spans="1:43">
       <c r="A33" s="1" t="s">
         <v>781</v>
       </c>
@@ -8433,110 +8621,113 @@
       <c r="E33" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="F33" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="J33" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="O33" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P33" s="2" t="s">
+      <c r="Q33" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="R33" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R33" s="2" t="s">
+      <c r="S33" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="S33" s="2" t="s">
+      <c r="T33" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="T33" s="2" t="s">
+      <c r="U33" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="V33" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="V33" s="2" t="s">
+      <c r="W33" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="W33" s="2" t="s">
+      <c r="X33" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="X33" s="2" t="s">
+      <c r="Y33" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="Y33" s="2" t="s">
+      <c r="Z33" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Z33" s="2" t="s">
+      <c r="AA33" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="AA33" s="2" t="s">
+      <c r="AB33" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="AB33" s="2" t="s">
+      <c r="AC33" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="AC33" s="2" t="s">
+      <c r="AD33" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="AD33" s="2" t="s">
+      <c r="AE33" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="AE33" s="1" t="s">
+      <c r="AF33" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="AF33" s="2" t="s">
+      <c r="AG33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG33" s="2" t="s">
+      <c r="AH33" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="AH33" s="2" t="s">
+      <c r="AI33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI33" s="2" t="s">
+      <c r="AJ33" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ33" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK33" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM33" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="AM33" s="2" t="s">
+      <c r="AN33" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AN33" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP33" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP33" s="2" t="s">
+      <c r="AQ33" s="2" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="34" spans="1:42" ht="21">
+    <row r="34" spans="1:43" ht="21">
       <c r="A34" s="1" t="s">
         <v>482</v>
       </c>
@@ -8552,110 +8743,113 @@
       <c r="E34" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="L34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P34" s="2" t="s">
+      <c r="Q34" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="R34" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R34" s="2" t="s">
+      <c r="S34" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="T34" s="11" t="s">
         <v>690</v>
       </c>
-      <c r="T34" s="2" t="s">
+      <c r="U34" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="U34" s="2" t="s">
+      <c r="V34" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="V34" s="2" t="s">
+      <c r="W34" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="W34" s="2" t="s">
+      <c r="X34" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="X34" s="2" t="s">
+      <c r="Y34" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="Y34" s="8">
+      <c r="Z34" s="8">
         <v>0.32</v>
       </c>
-      <c r="Z34" s="2" t="s">
+      <c r="AA34" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="AA34" s="7">
+      <c r="AB34" s="7">
         <v>0.4622</v>
       </c>
-      <c r="AB34" s="2" t="s">
+      <c r="AC34" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC34" s="2" t="s">
+      <c r="AD34" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="AD34" s="2" t="s">
+      <c r="AE34" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE34" s="1" t="s">
+      <c r="AF34" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="AF34" s="2" t="s">
+      <c r="AG34" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG34" s="2" t="s">
+      <c r="AH34" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="AH34" s="2" t="s">
+      <c r="AI34" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI34" s="2" t="s">
+      <c r="AJ34" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="AJ34" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK34" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM34" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="AM34" s="2" t="s">
+      <c r="AN34" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="AN34" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP34" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP34" s="2" t="s">
+      <c r="AQ34" s="2" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="35" spans="1:42">
+    <row r="35" spans="1:43">
       <c r="A35" s="1" t="s">
         <v>485</v>
       </c>
@@ -8671,110 +8865,113 @@
       <c r="E35" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="J35" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="J35" s="8">
+      <c r="K35" s="8">
         <v>0.75</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="L35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L35" s="2" t="s">
+      <c r="M35" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="O35" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P35" s="2" t="s">
+      <c r="Q35" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="R35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R35" s="2" t="s">
+      <c r="S35" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="S35" s="2" t="s">
+      <c r="T35" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="T35" s="2" t="s">
+      <c r="U35" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="U35" s="2" t="s">
+      <c r="V35" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="V35" s="2" t="s">
+      <c r="W35" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="W35" s="2" t="s">
+      <c r="X35" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="X35" s="2" t="s">
+      <c r="Y35" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="Y35" s="7">
+      <c r="Z35" s="7">
         <v>0.33</v>
       </c>
-      <c r="Z35" s="2" t="s">
+      <c r="AA35" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="AA35" s="7" t="s">
+      <c r="AB35" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="AB35" s="2" t="s">
+      <c r="AC35" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="AC35" s="7" t="s">
+      <c r="AD35" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="AD35" s="2" t="s">
+      <c r="AE35" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="AE35" s="1" t="s">
+      <c r="AF35" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="AF35" s="2" t="s">
+      <c r="AG35" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG35" s="2" t="s">
+      <c r="AH35" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="AH35" s="2" t="s">
+      <c r="AI35" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI35" s="2" t="s">
+      <c r="AJ35" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ35" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK35" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM35" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="AM35" s="2" t="s">
+      <c r="AN35" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="AN35" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP35" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP35" s="2" t="s">
+      <c r="AQ35" s="2" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="36" spans="1:42" ht="16">
+    <row r="36" spans="1:43" ht="16">
       <c r="A36" s="1" t="s">
         <v>502</v>
       </c>
@@ -8790,110 +8987,113 @@
       <c r="E36" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="F36" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="L36" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="O36" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="P36" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P36" s="2" t="s">
+      <c r="Q36" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="R36" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R36" s="2" t="s">
+      <c r="S36" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="T36" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="U36" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="U36" s="2" t="s">
+      <c r="V36" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="V36" s="2" t="s">
+      <c r="W36" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="W36" s="2" t="s">
+      <c r="X36" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="X36" s="2" t="s">
+      <c r="Y36" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="Y36" s="7">
+      <c r="Z36" s="7">
         <v>0.3327</v>
       </c>
-      <c r="Z36" s="2" t="s">
+      <c r="AA36" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="AA36" s="7">
+      <c r="AB36" s="7">
         <v>0.38300000000000001</v>
       </c>
-      <c r="AB36" s="2" t="s">
+      <c r="AC36" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="AC36" s="7" t="s">
+      <c r="AD36" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="AD36" s="2" t="s">
+      <c r="AE36" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="AE36" s="1" t="s">
+      <c r="AF36" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF36" s="2" t="s">
+      <c r="AG36" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG36" s="2" t="s">
+      <c r="AH36" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="AH36" s="2" t="s">
+      <c r="AI36" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI36" s="2" t="s">
+      <c r="AJ36" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AJ36" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK36" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM36" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="AM36" s="2" t="s">
+      <c r="AN36" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="AN36" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO36" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP36" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP36" s="2" t="s">
+      <c r="AQ36" s="2" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="37" spans="1:42">
+    <row r="37" spans="1:43">
       <c r="A37" s="1" t="s">
         <v>521</v>
       </c>
@@ -8909,110 +9109,113 @@
       <c r="E37" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="F37" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="J37" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="L37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="O37" s="2" t="s">
+      <c r="P37" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="P37" s="2" t="s">
+      <c r="Q37" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="R37" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R37" s="2" t="s">
+      <c r="S37" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="S37" s="2" t="s">
+      <c r="T37" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="T37" s="2" t="s">
+      <c r="U37" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="U37" s="2" t="s">
+      <c r="V37" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="V37" s="2" t="s">
+      <c r="W37" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="W37" s="2" t="s">
+      <c r="X37" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="X37" s="2" t="s">
+      <c r="Y37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Y37" s="2" t="s">
+      <c r="Z37" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z37" s="2" t="s">
+      <c r="AA37" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="AA37" s="2" t="s">
+      <c r="AB37" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="AB37" s="2" t="s">
+      <c r="AC37" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="AC37" s="2" t="s">
+      <c r="AD37" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="AD37" s="2" t="s">
+      <c r="AE37" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE37" s="1" t="s">
+      <c r="AF37" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="AF37" s="2" t="s">
+      <c r="AG37" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG37" s="2" t="s">
+      <c r="AH37" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="AH37" s="2" t="s">
+      <c r="AI37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI37" s="2" t="s">
+      <c r="AJ37" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AJ37" s="2" t="s">
+      <c r="AK37" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="AK37" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AL37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM37" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="AM37" s="2" t="s">
+      <c r="AN37" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AN37" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP37" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP37" s="2" t="s">
+      <c r="AQ37" s="2" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="38" spans="1:42">
+    <row r="38" spans="1:43">
       <c r="A38" s="1" t="s">
         <v>537</v>
       </c>
@@ -9028,110 +9231,113 @@
       <c r="E38" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="F38" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="L38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L38" s="2" t="s">
+      <c r="M38" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="O38" s="2" t="s">
+      <c r="P38" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P38" s="2" t="s">
+      <c r="Q38" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="R38" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="R38" s="2" t="s">
+      <c r="S38" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="S38" s="2" t="s">
+      <c r="T38" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="T38" s="2" t="s">
+      <c r="U38" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="U38" s="2" t="s">
+      <c r="V38" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>410</v>
       </c>
       <c r="X38" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Y38" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="Y38" s="2" t="s">
+      <c r="Z38" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="Z38" s="2" t="s">
+      <c r="AA38" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="AA38" s="7">
+      <c r="AB38" s="7">
         <v>0.46150000000000002</v>
       </c>
-      <c r="AB38" s="2" t="s">
+      <c r="AC38" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="AC38" s="2" t="s">
+      <c r="AD38" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="AD38" s="2" t="s">
+      <c r="AE38" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE38" s="1">
+      <c r="AF38" s="1">
         <v>7.0682870370370376E-4</v>
       </c>
-      <c r="AF38" s="2" t="s">
+      <c r="AG38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG38" s="2" t="s">
+      <c r="AH38" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="AH38" s="2" t="s">
+      <c r="AI38" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI38" s="2" t="s">
+      <c r="AJ38" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AJ38" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK38" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM38" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="AM38" s="2" t="s">
+      <c r="AN38" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="AN38" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO38" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP38" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP38" s="2" t="s">
+      <c r="AQ38" s="2" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="39" spans="1:42">
+    <row r="39" spans="1:43">
       <c r="A39" s="1" t="s">
         <v>793</v>
       </c>
@@ -9147,110 +9353,113 @@
       <c r="E39" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="F39" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="J39" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="K39" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L39" s="2" t="s">
+      <c r="M39" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="O39" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="O39" s="2" t="s">
+      <c r="P39" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P39" s="2" t="s">
+      <c r="Q39" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="R39" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="R39" s="2" t="s">
+      <c r="S39" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="S39" s="2" t="s">
+      <c r="T39" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="T39" s="2" t="s">
+      <c r="U39" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="U39" s="2" t="s">
+      <c r="V39" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="V39" s="2" t="s">
+      <c r="W39" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="W39" s="2" t="s">
+      <c r="X39" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="X39" s="2" t="s">
+      <c r="Y39" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="Y39" s="7">
+      <c r="Z39" s="7">
         <v>0.32100000000000001</v>
       </c>
-      <c r="Z39" s="2" t="s">
+      <c r="AA39" s="2" t="s">
         <v>932</v>
       </c>
-      <c r="AA39" s="7">
+      <c r="AB39" s="7">
         <v>0.51349999999999996</v>
       </c>
-      <c r="AB39" s="9" t="s">
+      <c r="AC39" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="AC39" s="2" t="s">
+      <c r="AD39" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="AD39" s="2" t="s">
+      <c r="AE39" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="AE39" s="1" t="s">
+      <c r="AF39" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AF39" s="2" t="s">
+      <c r="AG39" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG39" s="2" t="s">
+      <c r="AH39" s="2" t="s">
         <v>925</v>
       </c>
-      <c r="AH39" s="2" t="s">
+      <c r="AI39" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI39" s="2" t="s">
+      <c r="AJ39" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AJ39" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK39" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM39" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="AM39" s="2" t="s">
+      <c r="AN39" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="AN39" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP39" s="2" t="s">
         <v>1005</v>
       </c>
-      <c r="AP39" s="2" t="s">
+      <c r="AQ39" s="2" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="40" spans="1:42">
+    <row r="40" spans="1:43">
       <c r="A40" s="1" t="s">
         <v>910</v>
       </c>
@@ -9266,92 +9475,95 @@
       <c r="E40" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="F40" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="K40" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="M40" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="O40" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="O40" s="2" t="s">
+      <c r="P40" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P40" s="2" t="s">
+      <c r="Q40" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q40" s="2" t="s">
+      <c r="R40" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>916</v>
       </c>
       <c r="S40" s="2" t="s">
         <v>916</v>
       </c>
       <c r="T40" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="U40" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="U40" s="2" t="s">
+      <c r="V40" s="2" t="s">
         <v>918</v>
       </c>
-      <c r="V40" s="2" t="s">
+      <c r="W40" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="W40" s="2" t="s">
+      <c r="X40" s="2" t="s">
         <v>920</v>
       </c>
-      <c r="X40" s="2" t="s">
+      <c r="Y40" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="Y40" s="7">
+      <c r="Z40" s="7">
         <v>0.32500000000000001</v>
       </c>
-      <c r="Z40" s="2" t="s">
+      <c r="AA40" s="2" t="s">
         <v>922</v>
       </c>
-      <c r="AA40" s="7">
+      <c r="AB40" s="7">
         <v>0.45660000000000001</v>
       </c>
-      <c r="AB40" s="2" t="s">
+      <c r="AC40" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="AC40" s="7" t="s">
+      <c r="AD40" s="7" t="s">
         <v>923</v>
       </c>
-      <c r="AD40" s="2" t="s">
+      <c r="AE40" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="AE40" s="1" t="s">
+      <c r="AF40" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="AF40" s="2" t="s">
+      <c r="AG40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG40" s="2" t="s">
+      <c r="AH40" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="AH40" s="2" t="s">
+      <c r="AI40" s="2" t="s">
         <v>929</v>
       </c>
-      <c r="AI40" s="2" t="s">
+      <c r="AJ40" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AO40" s="2" t="s">
+      <c r="AP40" s="2" t="s">
         <v>1005</v>
       </c>
     </row>
-    <row r="41" spans="1:42">
+    <row r="41" spans="1:43">
       <c r="A41" s="1" t="s">
         <v>976</v>
       </c>
@@ -9367,101 +9579,104 @@
       <c r="E41" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="F41" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="L41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="O41" s="2" t="s">
         <v>983</v>
       </c>
-      <c r="O41" s="2" t="s">
+      <c r="P41" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P41" s="2" t="s">
+      <c r="Q41" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q41" s="2" t="s">
+      <c r="R41" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="R41" s="2" t="s">
+      <c r="S41" s="2" t="s">
         <v>985</v>
       </c>
-      <c r="S41" s="2" t="s">
+      <c r="T41" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="T41" s="2" t="s">
+      <c r="U41" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="U41" s="2" t="s">
+      <c r="V41" s="2" t="s">
         <v>988</v>
       </c>
-      <c r="V41" s="2" t="s">
+      <c r="W41" s="2" t="s">
         <v>989</v>
       </c>
-      <c r="W41" s="2" t="s">
+      <c r="X41" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="X41" s="2" t="s">
+      <c r="Y41" s="2" t="s">
         <v>990</v>
       </c>
-      <c r="Y41" s="7">
+      <c r="Z41" s="7">
         <v>0.33900000000000002</v>
       </c>
-      <c r="Z41" s="2" t="s">
+      <c r="AA41" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="AA41" s="7">
+      <c r="AB41" s="7">
         <v>0.50270000000000004</v>
       </c>
-      <c r="AB41" s="2" t="s">
+      <c r="AC41" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC41" s="7" t="s">
+      <c r="AD41" s="7" t="s">
         <v>992</v>
       </c>
-      <c r="AD41" s="2" t="s">
+      <c r="AE41" s="2" t="s">
         <v>993</v>
       </c>
-      <c r="AE41" s="1" t="s">
+      <c r="AF41" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="AF41" s="2" t="s">
+      <c r="AG41" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG41" s="2" t="s">
+      <c r="AH41" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="AH41" s="2" t="s">
+      <c r="AI41" s="2" t="s">
         <v>996</v>
       </c>
-      <c r="AI41" s="2" t="s">
+      <c r="AJ41" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="AL41" s="2" t="s">
+      <c r="AM41" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="AM41" s="2" t="s">
+      <c r="AN41" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="AN41" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP41" s="2" t="s">
         <v>1005</v>
       </c>
     </row>
-    <row r="42" spans="1:42">
+    <row r="42" spans="1:43">
       <c r="A42" s="1" t="s">
         <v>783</v>
       </c>
@@ -9478,112 +9693,115 @@
         <v>636</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="K42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="O42" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="O42" s="2" t="s">
+      <c r="P42" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P42" s="2" t="s">
+      <c r="Q42" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q42" s="2" t="s">
+      <c r="R42" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="S42" s="2" t="s">
         <v>641</v>
       </c>
       <c r="T42" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="U42" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="U42" s="2" t="s">
+      <c r="V42" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="V42" s="2" t="s">
+      <c r="W42" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="W42" s="2" t="s">
+      <c r="X42" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="X42" s="2" t="s">
+      <c r="Y42" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="Y42" s="8">
+      <c r="Z42" s="8">
         <v>0.33</v>
       </c>
-      <c r="Z42" s="2" t="s">
+      <c r="AA42" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="AA42" s="7">
+      <c r="AB42" s="7">
         <v>0.57020000000000004</v>
       </c>
-      <c r="AB42" s="2" t="s">
+      <c r="AC42" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="AC42" s="2" t="s">
+      <c r="AD42" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="AD42" s="2" t="s">
+      <c r="AE42" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="AE42" s="1" t="s">
+      <c r="AF42" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="AF42" s="2" t="s">
+      <c r="AG42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG42" s="2" t="s">
+      <c r="AH42" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="AH42" s="2" t="s">
+      <c r="AI42" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI42" s="2" t="s">
+      <c r="AJ42" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="AJ42" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK42" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM42" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="AM42" s="2" t="s">
+      <c r="AN42" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="AN42" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO42" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP42" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="AP42" s="2" t="s">
+      <c r="AQ42" s="2" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="43" spans="1:42" ht="16">
+    <row r="43" spans="1:43" ht="16">
       <c r="A43" s="1" t="s">
         <v>782</v>
       </c>
@@ -9599,110 +9817,113 @@
       <c r="E43" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="F43" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="L43" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="O43" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="O43" s="2" t="s">
+      <c r="P43" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P43" s="2" t="s">
+      <c r="Q43" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="R43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R43" s="2" t="s">
+      <c r="S43" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="S43" s="2" t="s">
+      <c r="T43" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="T43" s="2" t="s">
+      <c r="U43" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="U43" s="2" t="s">
+      <c r="V43" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="V43" s="2" t="s">
+      <c r="W43" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="W43" s="2" t="s">
+      <c r="X43" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="X43" s="2" t="s">
+      <c r="Y43" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="Y43" s="7">
+      <c r="Z43" s="7">
         <v>0.33500000000000002</v>
       </c>
-      <c r="Z43" s="2" t="s">
+      <c r="AA43" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="AA43" s="7">
+      <c r="AB43" s="7">
         <v>0.49540000000000001</v>
       </c>
-      <c r="AB43" s="2" t="s">
+      <c r="AC43" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="AC43" s="7" t="s">
+      <c r="AD43" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="AD43" s="2" t="s">
+      <c r="AE43" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="AE43" s="1" t="s">
+      <c r="AF43" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="AF43" s="2" t="s">
+      <c r="AG43" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG43" s="2" t="s">
+      <c r="AH43" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="AH43" s="2" t="s">
+      <c r="AI43" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI43" s="2" t="s">
+      <c r="AJ43" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="AJ43" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK43" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM43" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="AM43" s="2" t="s">
+      <c r="AN43" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="AN43" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO43" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP43" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="AP43" s="2" t="s">
+      <c r="AQ43" s="2" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="44" spans="1:42">
+    <row r="44" spans="1:43">
       <c r="A44" s="1" t="s">
         <v>784</v>
       </c>
@@ -9718,107 +9939,110 @@
       <c r="E44" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="F44" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="K44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="O44" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="O44" s="2" t="s">
+      <c r="P44" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P44" s="2" t="s">
+      <c r="Q44" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q44" s="2" t="s">
+      <c r="R44" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R44" s="2" t="s">
+      <c r="S44" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="S44" s="2" t="s">
+      <c r="T44" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="T44" s="2" t="s">
+      <c r="U44" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="U44" s="2" t="s">
+      <c r="V44" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="V44" s="2" t="s">
+      <c r="W44" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="W44" s="2" t="s">
+      <c r="X44" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="X44" s="2" t="s">
+      <c r="Y44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Y44" s="2" t="s">
+      <c r="Z44" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z44" s="2" t="s">
+      <c r="AA44" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="AA44" s="2" t="s">
+      <c r="AB44" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="AB44" s="2" t="s">
+      <c r="AC44" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="AC44" s="2" t="s">
+      <c r="AD44" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AD44" s="2" t="s">
+      <c r="AE44" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AE44" s="1" t="s">
+      <c r="AF44" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="AF44" s="2" t="s">
+      <c r="AG44" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG44" s="2" t="s">
+      <c r="AH44" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="AH44" s="2" t="s">
+      <c r="AI44" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI44" s="2" t="s">
+      <c r="AJ44" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AJ44" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AK44" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AL44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM44" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="AM44" s="2" t="s">
+      <c r="AN44" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="AN44" s="2" t="s">
+      <c r="AO44" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="AO44" s="2" t="s">
+      <c r="AP44" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="AP44" s="2" t="s">
+      <c r="AQ44" s="2" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="45" spans="1:42" ht="19">
+    <row r="45" spans="1:43" ht="19">
       <c r="A45" s="1" t="s">
         <v>794</v>
       </c>
@@ -9834,101 +10058,104 @@
       <c r="E45" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="F45" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="J45" s="2" t="s">
         <v>885</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="K45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="L45" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="O45" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="O45" s="2" t="s">
+      <c r="P45" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P45" s="2" t="s">
+      <c r="Q45" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q45" s="2" t="s">
+      <c r="R45" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>887</v>
       </c>
       <c r="S45" s="2" t="s">
         <v>887</v>
       </c>
       <c r="T45" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="U45" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="U45" s="2" t="s">
+      <c r="V45" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="V45" s="2" t="s">
+      <c r="W45" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="W45" s="2" t="s">
+      <c r="X45" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="X45" s="2" t="s">
+      <c r="Y45" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="Y45" s="7">
+      <c r="Z45" s="7">
         <v>0.315</v>
       </c>
-      <c r="Z45" s="2" t="s">
+      <c r="AA45" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="AA45" s="7">
+      <c r="AB45" s="7">
         <v>0.45700000000000002</v>
       </c>
-      <c r="AB45" s="2" t="s">
+      <c r="AC45" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="AC45" s="7" t="s">
+      <c r="AD45" s="7" t="s">
         <v>894</v>
       </c>
-      <c r="AD45" s="2" t="s">
+      <c r="AE45" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="AE45" s="1" t="s">
+      <c r="AF45" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="AF45" s="2" t="s">
+      <c r="AG45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG45" s="2" t="s">
+      <c r="AH45" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="AH45" s="2" t="s">
+      <c r="AI45" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI45" s="2" t="s">
+      <c r="AJ45" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AL45" s="12" t="s">
+      <c r="AM45" s="12" t="s">
         <v>897</v>
       </c>
-      <c r="AM45" s="2" t="s">
+      <c r="AN45" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="AN45" s="2" t="s">
+      <c r="AO45" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="AO45" s="2" t="s">
+      <c r="AP45" s="2" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="46" spans="1:42">
+    <row r="46" spans="1:43">
       <c r="A46" s="1" t="s">
         <v>869</v>
       </c>
@@ -9945,112 +10172,115 @@
         <v>852</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>948</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="H46" s="9" t="s">
         <v>947</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="J46" s="2" t="s">
         <v>853</v>
       </c>
-      <c r="J46" s="2" t="s">
+      <c r="K46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="L46" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="O46" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="O46" s="2" t="s">
+      <c r="P46" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="P46" s="2" t="s">
+      <c r="Q46" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="R46" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R46" s="2" t="s">
+      <c r="S46" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="S46" s="2" t="s">
+      <c r="T46" s="2" t="s">
         <v>858</v>
       </c>
-      <c r="T46" s="2" t="s">
+      <c r="U46" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="U46" s="2" t="s">
+      <c r="V46" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="V46" s="2" t="s">
+      <c r="W46" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="W46" s="2" t="s">
+      <c r="X46" s="2" t="s">
         <v>859</v>
       </c>
-      <c r="X46" s="2" t="s">
+      <c r="Y46" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="Y46" s="8">
+      <c r="Z46" s="8">
         <v>0.32</v>
       </c>
-      <c r="Z46" s="2" t="s">
+      <c r="AA46" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="AA46" s="7">
+      <c r="AB46" s="7">
         <v>0.38140000000000002</v>
       </c>
-      <c r="AB46" s="2" t="s">
+      <c r="AC46" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="AC46" s="2" t="s">
+      <c r="AD46" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="AD46" s="2" t="s">
+      <c r="AE46" s="2" t="s">
         <v>864</v>
       </c>
-      <c r="AE46" s="1" t="s">
+      <c r="AF46" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="AF46" s="2" t="s">
+      <c r="AG46" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG46" s="2" t="s">
+      <c r="AH46" s="2" t="s">
         <v>865</v>
       </c>
-      <c r="AH46" s="2" t="s">
+      <c r="AI46" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI46" s="2" t="s">
+      <c r="AJ46" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AK46" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AL46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM46" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="AM46" s="2" t="s">
+      <c r="AN46" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="AN46" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="AO46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP46" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="AP46" s="2" t="s">
+      <c r="AQ46" s="2" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="47" spans="1:42">
+    <row r="47" spans="1:43">
       <c r="A47" s="1" t="s">
         <v>871</v>
       </c>
@@ -10067,79 +10297,82 @@
         <v>1053</v>
       </c>
       <c r="F47" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>945</v>
       </c>
-      <c r="J47" s="2" t="s">
+      <c r="K47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="L47" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>1063</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="O47" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="O47" s="2" t="s">
+      <c r="P47" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="P47" s="2" t="s">
+      <c r="Q47" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q47" s="2" t="s">
+      <c r="R47" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>905</v>
       </c>
       <c r="S47" s="2" t="s">
         <v>905</v>
       </c>
       <c r="T47" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="U47" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="U47" s="2" t="s">
+      <c r="V47" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="Y47" s="8">
+      <c r="Z47" s="8">
         <v>0.15</v>
       </c>
-      <c r="Z47" s="2" t="s">
+      <c r="AA47" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="AB47" s="2" t="s">
+      <c r="AC47" s="2" t="s">
         <v>1060</v>
       </c>
-      <c r="AC47" s="7" t="s">
+      <c r="AD47" s="7" t="s">
         <v>1062</v>
       </c>
-      <c r="AF47" s="2" t="s">
+      <c r="AG47" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG47" s="2" t="s">
+      <c r="AH47" s="2" t="s">
         <v>1064</v>
       </c>
-      <c r="AH47" s="2" t="s">
+      <c r="AI47" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI47" s="2" t="s">
+      <c r="AJ47" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AO47" s="2" t="s">
+      <c r="AP47" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="AP47" s="2" t="s">
+      <c r="AQ47" s="2" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="48" spans="1:42">
+    <row r="48" spans="1:43">
       <c r="A48" s="1" t="s">
         <v>872</v>
       </c>
@@ -10156,79 +10389,82 @@
         <v>1054</v>
       </c>
       <c r="F48" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="H48" s="9" t="s">
         <v>943</v>
       </c>
-      <c r="I48" s="2" t="s">
+      <c r="J48" s="2" t="s">
         <v>1070</v>
       </c>
-      <c r="J48" s="2" t="s">
+      <c r="K48" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="L48" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="O48" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="O48" s="2" t="s">
+      <c r="P48" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="P48" s="2" t="s">
+      <c r="Q48" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q48" s="2" t="s">
+      <c r="R48" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R48" s="2" t="s">
+      <c r="S48" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="U48" s="2" t="s">
+      <c r="V48" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="W48" s="2" t="s">
+      <c r="X48" s="2" t="s">
         <v>1066</v>
       </c>
-      <c r="Y48" s="7">
+      <c r="Z48" s="7">
         <v>0.29899999999999999</v>
       </c>
-      <c r="Z48" s="2" t="s">
+      <c r="AA48" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="AB48" s="2" t="s">
+      <c r="AC48" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="AC48" s="7" t="s">
+      <c r="AD48" s="7" t="s">
         <v>1069</v>
       </c>
-      <c r="AD48" s="2" t="s">
+      <c r="AE48" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="AF48" s="2" t="s">
+      <c r="AG48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AG48" s="2" t="s">
+      <c r="AH48" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="AH48" s="2" t="s">
+      <c r="AI48" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI48" s="2" t="s">
+      <c r="AJ48" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AO48" s="2" t="s">
+      <c r="AP48" s="2" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="49" spans="1:42">
+    <row r="49" spans="1:43">
       <c r="A49" s="1" t="s">
         <v>873</v>
       </c>
@@ -10245,61 +10481,64 @@
         <v>1055</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>941</v>
       </c>
-      <c r="J49" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="L49" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="O49" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="O49" s="2" t="s">
+      <c r="P49" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="P49" s="2" t="s">
+      <c r="Q49" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q49" s="2" t="s">
+      <c r="R49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R49" s="2" t="s">
+      <c r="S49" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="U49" s="2" t="s">
+      <c r="V49" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="Z49" s="2" t="s">
+      <c r="AA49" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="AF49" s="2" t="s">
+      <c r="AG49" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AH49" s="2" t="s">
+      <c r="AI49" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI49" s="2" t="s">
+      <c r="AJ49" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AO49" s="2" t="s">
+      <c r="AP49" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="AP49" s="2" t="s">
+      <c r="AQ49" s="2" t="s">
         <v>1048</v>
       </c>
     </row>
-    <row r="50" spans="1:42">
+    <row r="50" spans="1:43">
       <c r="A50" s="1" t="s">
         <v>874</v>
       </c>
@@ -10316,59 +10555,62 @@
         <v>1056</v>
       </c>
       <c r="F50" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="H50" s="9" t="s">
         <v>939</v>
       </c>
-      <c r="J50" s="2" t="s">
+      <c r="K50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="L50" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="M50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M50" s="2" t="s">
+      <c r="N50" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="O50" s="2" t="s">
         <v>1058</v>
       </c>
-      <c r="O50" s="2" t="s">
+      <c r="P50" s="2" t="s">
         <v>1059</v>
       </c>
-      <c r="P50" s="2" t="s">
+      <c r="Q50" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="Q50" s="2" t="s">
+      <c r="R50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="R50" s="2" t="s">
+      <c r="S50" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="U50" s="2" t="s">
+      <c r="V50" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="Z50" s="2" t="s">
+      <c r="AA50" s="2" t="s">
         <v>1061</v>
       </c>
-      <c r="AF50" s="2" t="s">
+      <c r="AG50" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AH50" s="2" t="s">
+      <c r="AI50" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AI50" s="2" t="s">
+      <c r="AJ50" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="AO50" s="2" t="s">
+      <c r="AP50" s="2" t="s">
         <v>1007</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AN44">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AO44">
     <sortCondition ref="A2:A44"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -10419,29 +10661,29 @@
     <hyperlink ref="D49" r:id="rId44" xr:uid="{A3A70E41-D9C4-D74F-BF46-406D278A338D}"/>
     <hyperlink ref="D50" r:id="rId45" xr:uid="{70FDDF65-CF5C-204D-A285-F382553E7D5E}"/>
     <hyperlink ref="D40" r:id="rId46" xr:uid="{013869AD-3839-9949-BD78-138181727368}"/>
-    <hyperlink ref="AB39" r:id="rId47" location=":~:text=%E6%A8%93%E5%B1%A4%E8%A6%8F%E5%8A%83%EF%BC%9A-,%E5%9C%B0%E4%B8%8A14%E5%B1%A4%EF%BC%8C%E5%9C%B0%E4%B8%8B4%E5%B1%A4,-%E8%BB%8A%E4%BD%8D%E8%A6%8F%E5%8A%83%EF%BC%9A" xr:uid="{1D7C1FF6-699C-3D42-9FD6-E803B0EB879E}"/>
-    <hyperlink ref="G50" r:id="rId48" xr:uid="{45E5744C-2297-5249-919F-E8100A7412C2}"/>
-    <hyperlink ref="G49" r:id="rId49" xr:uid="{2ABBD1D3-4997-E643-B81B-99C7652DBF8E}"/>
-    <hyperlink ref="G48" r:id="rId50" xr:uid="{A9611226-F1F2-8845-B4F2-E24216072372}"/>
-    <hyperlink ref="G47" r:id="rId51" xr:uid="{7EC0A553-B3B8-7F44-9C11-54ED356A5137}"/>
-    <hyperlink ref="G46" r:id="rId52" xr:uid="{5EFC57F9-D69B-CD4C-B170-34B84F99466D}"/>
-    <hyperlink ref="G32" r:id="rId53" xr:uid="{D5178C7D-72D8-1C45-A46F-C5BE87520D74}"/>
-    <hyperlink ref="G28" r:id="rId54" xr:uid="{C439EE12-B738-614D-9659-C664A5927CDF}"/>
-    <hyperlink ref="G27" r:id="rId55" xr:uid="{B5963B89-4E6B-BE4A-BFF9-C91A4C5DD556}"/>
-    <hyperlink ref="G24" r:id="rId56" xr:uid="{78663025-8F04-F842-9C43-15B19CD89A27}"/>
-    <hyperlink ref="G20" r:id="rId57" xr:uid="{F9795351-78C0-5647-B13A-6B9CA2A4852F}"/>
-    <hyperlink ref="G19" r:id="rId58" xr:uid="{E9E739D1-05BF-0143-94D3-A8770BAC0EC3}"/>
-    <hyperlink ref="G13" r:id="rId59" xr:uid="{E2EBE5B8-46EF-F444-83C1-DC75351B9475}"/>
-    <hyperlink ref="G12" r:id="rId60" xr:uid="{BCDE8407-65EE-BF42-90E3-D19E9AE73C6B}"/>
-    <hyperlink ref="G8" r:id="rId61" xr:uid="{72D8EA79-1383-EE44-AA01-F26EFCD2CD24}"/>
-    <hyperlink ref="G5" r:id="rId62" xr:uid="{F3D01D5C-AFFF-264E-A582-4DD0DDFC84C7}"/>
-    <hyperlink ref="G4" r:id="rId63" xr:uid="{84C54EA4-D033-AC43-947A-36013AC503E3}"/>
+    <hyperlink ref="AC39" r:id="rId47" location=":~:text=%E6%A8%93%E5%B1%A4%E8%A6%8F%E5%8A%83%EF%BC%9A-,%E5%9C%B0%E4%B8%8A14%E5%B1%A4%EF%BC%8C%E5%9C%B0%E4%B8%8B4%E5%B1%A4,-%E8%BB%8A%E4%BD%8D%E8%A6%8F%E5%8A%83%EF%BC%9A" xr:uid="{1D7C1FF6-699C-3D42-9FD6-E803B0EB879E}"/>
+    <hyperlink ref="H50" r:id="rId48" xr:uid="{45E5744C-2297-5249-919F-E8100A7412C2}"/>
+    <hyperlink ref="H49" r:id="rId49" xr:uid="{2ABBD1D3-4997-E643-B81B-99C7652DBF8E}"/>
+    <hyperlink ref="H48" r:id="rId50" xr:uid="{A9611226-F1F2-8845-B4F2-E24216072372}"/>
+    <hyperlink ref="H47" r:id="rId51" xr:uid="{7EC0A553-B3B8-7F44-9C11-54ED356A5137}"/>
+    <hyperlink ref="H46" r:id="rId52" xr:uid="{5EFC57F9-D69B-CD4C-B170-34B84F99466D}"/>
+    <hyperlink ref="H32" r:id="rId53" xr:uid="{D5178C7D-72D8-1C45-A46F-C5BE87520D74}"/>
+    <hyperlink ref="H28" r:id="rId54" xr:uid="{C439EE12-B738-614D-9659-C664A5927CDF}"/>
+    <hyperlink ref="H27" r:id="rId55" xr:uid="{B5963B89-4E6B-BE4A-BFF9-C91A4C5DD556}"/>
+    <hyperlink ref="H24" r:id="rId56" xr:uid="{78663025-8F04-F842-9C43-15B19CD89A27}"/>
+    <hyperlink ref="H20" r:id="rId57" xr:uid="{F9795351-78C0-5647-B13A-6B9CA2A4852F}"/>
+    <hyperlink ref="H19" r:id="rId58" xr:uid="{E9E739D1-05BF-0143-94D3-A8770BAC0EC3}"/>
+    <hyperlink ref="H13" r:id="rId59" xr:uid="{E2EBE5B8-46EF-F444-83C1-DC75351B9475}"/>
+    <hyperlink ref="H12" r:id="rId60" xr:uid="{BCDE8407-65EE-BF42-90E3-D19E9AE73C6B}"/>
+    <hyperlink ref="H8" r:id="rId61" xr:uid="{72D8EA79-1383-EE44-AA01-F26EFCD2CD24}"/>
+    <hyperlink ref="H5" r:id="rId62" xr:uid="{F3D01D5C-AFFF-264E-A582-4DD0DDFC84C7}"/>
+    <hyperlink ref="H4" r:id="rId63" xr:uid="{84C54EA4-D033-AC43-947A-36013AC503E3}"/>
     <hyperlink ref="D41" r:id="rId64" xr:uid="{5D605B83-C0B5-6247-8E1F-76A070BB09FC}"/>
-    <hyperlink ref="AP13" r:id="rId65" xr:uid="{CFD41646-E757-ED43-ABA1-CABF00E32E92}"/>
-    <hyperlink ref="AP17" r:id="rId66" xr:uid="{15356CC6-D40A-6B4A-8042-A37FA29279E1}"/>
-    <hyperlink ref="AP32" r:id="rId67" xr:uid="{B01C4786-26E9-AD46-B1BA-AEA2C6C8405B}"/>
+    <hyperlink ref="AQ13" r:id="rId65" xr:uid="{CFD41646-E757-ED43-ABA1-CABF00E32E92}"/>
+    <hyperlink ref="AQ17" r:id="rId66" xr:uid="{15356CC6-D40A-6B4A-8042-A37FA29279E1}"/>
+    <hyperlink ref="AQ32" r:id="rId67" xr:uid="{B01C4786-26E9-AD46-B1BA-AEA2C6C8405B}"/>
     <hyperlink ref="D23" r:id="rId68" xr:uid="{E4A9568D-65A4-3F46-84D7-82A6B7BB96B6}"/>
-    <hyperlink ref="AP22" r:id="rId69" xr:uid="{E5A55661-5BE7-C748-BA92-C63CC5BD349D}"/>
+    <hyperlink ref="AQ22" r:id="rId69" xr:uid="{E5A55661-5BE7-C748-BA92-C63CC5BD349D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1101-House.xlsx
+++ b/db/A7XLK-1101-House.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3718B8A5-034F-5B4A-A1E1-C7FB03E2B50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE2EC38-AA1E-1943-A13F-E638DA8983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17080" yWindow="-13340" windowWidth="36360" windowHeight="13780" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="-16200" yWindow="-17820" windowWidth="36360" windowHeight="13780" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -3943,22 +3943,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2021/8:22.7萬元/坪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021/8:20.0萬元/坪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021/8:21.7萬元/坪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021/8:21.0萬元/坪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.youtube.com/channel/UC3jrCcov7boT9u2qDiezNrA?view_as=subscriber</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4220,6 +4204,22 @@
   </si>
   <si>
     <t>每坪開價2022</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22.7萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20.0萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.7萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.0萬元/坪</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4714,43 +4714,43 @@
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>1098</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>1072</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>1073</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="G1" s="13" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>1101</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J1" s="14" t="s">
+      <c r="N1" s="14" t="s">
+        <v>1074</v>
+      </c>
+      <c r="O1" s="14" t="s">
         <v>1075</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>1077</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>1103</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>1078</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>1079</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>1080</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>1081</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>935</v>
@@ -4878,7 +4878,7 @@
         <v>27.72</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="G2" s="15">
         <v>32.01</v>
@@ -4900,7 +4900,7 @@
         <v>28.5</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="N2" s="14">
         <v>34</v>
@@ -5051,7 +5051,7 @@
         <v>26</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="N3" s="14">
         <v>29</v>
@@ -5218,7 +5218,7 @@
         <v>26</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R4" s="9" t="s">
         <v>955</v>
@@ -5376,7 +5376,7 @@
         <v>25</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R5" s="9" t="s">
         <v>954</v>
@@ -5501,7 +5501,7 @@
         <v>22.84</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="G6" s="16">
         <v>26.27</v>
@@ -5536,7 +5536,7 @@
         <v>26</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>561</v>
@@ -5693,7 +5693,7 @@
         <v>27</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>116</v>
@@ -5837,7 +5837,7 @@
         <v>25.5</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="N8" s="14">
         <v>27</v>
@@ -5986,7 +5986,7 @@
         <v>32.5</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="N9" s="14">
         <v>44</v>
@@ -6118,7 +6118,7 @@
         <v>29.88</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G10" s="15">
         <v>37.450000000000003</v>
@@ -6140,7 +6140,7 @@
         <v>28.5</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="N10" s="14">
         <v>35</v>
@@ -6294,7 +6294,7 @@
         <v>27</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="N11" s="14">
         <v>26</v>
@@ -6307,7 +6307,7 @@
         <v>27</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>205</v>
@@ -6429,7 +6429,7 @@
         <v>24.17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="G12" s="13">
         <v>26.76</v>
@@ -6451,7 +6451,7 @@
         <v>25.5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="N12" s="14">
         <v>27</v>
@@ -6605,7 +6605,7 @@
         <v>31</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="N13" s="14">
         <v>38</v>
@@ -6773,7 +6773,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>243</v>
@@ -6895,7 +6895,7 @@
         <v>25.24</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="G15" s="15">
         <v>30.14</v>
@@ -6917,7 +6917,7 @@
         <v>30.5</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="N15" s="14">
         <v>35</v>
@@ -7060,7 +7060,7 @@
         <v>36.5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="N16" s="14">
         <v>38</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="4" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="G17" s="15">
         <v>28.96</v>
@@ -7225,7 +7225,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>157</v>
@@ -7347,7 +7347,7 @@
         <v>26.84</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G18" s="15">
         <v>34.33</v>
@@ -7369,7 +7369,7 @@
         <v>27</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="N18" s="14">
         <v>33</v>
@@ -7536,7 +7536,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R19" s="9" t="s">
         <v>949</v>
@@ -7683,7 +7683,7 @@
         <v>25</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="N20" s="14">
         <v>26</v>
@@ -7992,7 +7992,7 @@
         <v>30</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="N22" s="14">
         <v>34</v>
@@ -8104,7 +8104,7 @@
         <v>987</v>
       </c>
       <c r="BA22" s="9" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23" spans="1:53">
@@ -8156,7 +8156,7 @@
         <v>25</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>384</v>
@@ -8300,7 +8300,7 @@
         <v>30.5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="N24" s="14">
         <v>28</v>
@@ -8435,7 +8435,7 @@
         <v>24.76</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="G25" s="16">
         <v>29.05</v>
@@ -8457,7 +8457,7 @@
         <v>30</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="N25" s="14">
         <v>34</v>
@@ -8586,7 +8586,7 @@
         <v>25.71</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="G26" s="16">
         <v>31.03</v>
@@ -8608,7 +8608,7 @@
         <v>27</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="N26" s="14">
         <v>32</v>
@@ -8737,7 +8737,7 @@
         <v>26.45</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="G27" s="15">
         <v>28.89</v>
@@ -8759,7 +8759,7 @@
         <v>27</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="N27" s="14">
         <v>38</v>
@@ -9062,7 +9062,7 @@
         <v>36.5</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="N29" s="14">
         <v>45</v>
@@ -9216,7 +9216,7 @@
         <v>29.5</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="N30" s="14">
         <v>24</v>
@@ -9229,7 +9229,7 @@
         <v>24.5</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>464</v>
@@ -9351,7 +9351,7 @@
         <v>26.59</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="G31" s="16">
         <v>31.65</v>
@@ -9527,7 +9527,7 @@
         <v>28</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="N32" s="14">
         <v>30</v>
@@ -9662,7 +9662,7 @@
         <v>34.08</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="G33" s="15">
         <v>41.77</v>
@@ -9684,7 +9684,7 @@
         <v>35.5</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="N33" s="14">
         <v>44</v>
@@ -10274,7 +10274,7 @@
         <v>26.33</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G37" s="15">
         <v>28.67</v>
@@ -10296,7 +10296,7 @@
         <v>26</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="N37" s="14">
         <v>30</v>
@@ -10428,7 +10428,7 @@
         <v>27.47</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="G38" s="15">
         <v>32.229999999999997</v>
@@ -10450,7 +10450,7 @@
         <v>29.9</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="N38" s="14">
         <v>29.8</v>
@@ -10746,7 +10746,7 @@
         <v>33.5</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="N40" s="14">
         <v>35</v>
@@ -10860,7 +10860,7 @@
         <v>29.4</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="G41" s="15">
         <v>34.24</v>
@@ -11040,7 +11040,7 @@
         <v>35.5</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R42" s="2" t="s">
         <v>942</v>
@@ -11176,7 +11176,7 @@
         <v>41</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="N43" s="14">
         <v>45</v>
@@ -11343,7 +11343,7 @@
         <v>29</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>42</v>
@@ -11495,7 +11495,7 @@
         <v>30</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>884</v>
@@ -11643,7 +11643,7 @@
         <v>30</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R46" s="9" t="s">
         <v>941</v>
@@ -11774,7 +11774,7 @@
         <v>11.84</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1034</v>
+        <v>1100</v>
       </c>
       <c r="J47" s="14">
         <v>15</v>
@@ -11787,7 +11787,7 @@
         <v>15</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1034</v>
+        <v>1100</v>
       </c>
       <c r="N47" s="14">
         <v>15</v>
@@ -11800,7 +11800,7 @@
         <v>15</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R47" s="9" t="s">
         <v>940</v>
@@ -11812,16 +11812,16 @@
         <v>701</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="AA47" s="2" t="s">
         <v>768</v>
@@ -11845,19 +11845,19 @@
         <v>0.15</v>
       </c>
       <c r="AK47" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="AM47" s="2" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="AN47" s="7" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="AQ47" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR47" s="2" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="AS47" s="2" t="s">
         <v>63</v>
@@ -11898,7 +11898,7 @@
         <v>12.94</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1035</v>
+        <v>1101</v>
       </c>
       <c r="J48" s="14">
         <v>15</v>
@@ -11911,7 +11911,7 @@
         <v>15</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1035</v>
+        <v>1101</v>
       </c>
       <c r="N48" s="14">
         <v>15</v>
@@ -11924,13 +11924,13 @@
         <v>15</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R48" s="9" t="s">
         <v>939</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="U48" s="2" t="s">
         <v>42</v>
@@ -11939,16 +11939,16 @@
         <v>701</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="Z48" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="AA48" s="2" t="s">
         <v>768</v>
@@ -11963,19 +11963,19 @@
         <v>898</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="AJ48" s="7">
         <v>0.29899999999999999</v>
       </c>
       <c r="AK48" s="2" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="AM48" s="2" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="AN48" s="7" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="AO48" s="2" t="s">
         <v>592</v>
@@ -11984,7 +11984,7 @@
         <v>61</v>
       </c>
       <c r="AR48" s="2" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="AS48" s="2" t="s">
         <v>63</v>
@@ -12022,7 +12022,7 @@
         <v>13.62</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1036</v>
+        <v>1102</v>
       </c>
       <c r="J49" s="14">
         <v>15</v>
@@ -12035,7 +12035,7 @@
         <v>15</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1036</v>
+        <v>1102</v>
       </c>
       <c r="N49" s="14">
         <v>15</v>
@@ -12048,7 +12048,7 @@
         <v>15</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R49" s="9" t="s">
         <v>938</v>
@@ -12066,10 +12066,10 @@
         <v>44</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="AA49" s="2" t="s">
         <v>768</v>
@@ -12084,7 +12084,7 @@
         <v>899</v>
       </c>
       <c r="AK49" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="AQ49" s="2" t="s">
         <v>61</v>
@@ -12128,7 +12128,7 @@
         <v>14.83</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1037</v>
+        <v>1103</v>
       </c>
       <c r="J50" s="14">
         <v>15</v>
@@ -12141,7 +12141,7 @@
         <v>15</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1037</v>
+        <v>1103</v>
       </c>
       <c r="N50" s="14">
         <v>15</v>
@@ -12154,7 +12154,7 @@
         <v>15</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="R50" s="9" t="s">
         <v>937</v>
@@ -12172,10 +12172,10 @@
         <v>44</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="AA50" s="2" t="s">
         <v>768</v>
@@ -12190,7 +12190,7 @@
         <v>900</v>
       </c>
       <c r="AK50" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="AQ50" s="2" t="s">
         <v>61</v>

--- a/db/A7XLK-1101-House.xlsx
+++ b/db/A7XLK-1101-House.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE2EC38-AA1E-1943-A13F-E638DA8983B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC110A17-7C8D-804D-A0F0-8F0556A56051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16200" yWindow="-17820" windowWidth="36360" windowHeight="13780" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="-17020" yWindow="-14100" windowWidth="36360" windowHeight="13780" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1107">
   <si>
     <t>no</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1092,10 +1092,6 @@
     <t>欣時代</t>
   </si>
   <si>
-    <t>fig/AiCity-939-欣時代.jpg</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>https://newhouse.591.com.tw/home/housing/detail?hid=118905</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -3575,10 +3571,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>https://newhouse.591.com.tw/home/housing/info?hid=124978#:~:text=%E6%A8%93%E5%B1%A4%E8%A6%8F%E5%8A%83%EF%BC%9A-,%E5%9C%B0%E4%B8%8A14%E5%B1%A4%EF%BC%8C%E5%9C%B0%E4%B8%8B4%E5%B1%A4,-%E8%BB%8A%E4%BD%8D%E8%A6%8F%E5%8A%83%EF%BC%9A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>平面式136個</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4220,6 +4212,26 @@
   </si>
   <si>
     <t>21.0萬元/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>312</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>欣巴巴-欣時代</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-939-欣時代.jpeg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sale.591.com.tw/home/house/detail/2/10667288.html</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>33.47萬/坪</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4663,7 +4675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F89EF37-C3F3-8243-B091-96A26EC57E26}">
-  <dimension ref="A1:BA50"/>
+  <dimension ref="A1:BA51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="1"/>
@@ -4714,49 +4726,49 @@
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>1094</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="13" t="s">
         <v>1095</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="I1" s="2" t="s">
         <v>1096</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="J1" s="14" t="s">
+        <v>1069</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>1071</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>1098</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>1071</v>
-      </c>
-      <c r="K1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>1072</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>1073</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="N1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>1074</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="Q1" s="14" t="s">
         <v>1075</v>
       </c>
-      <c r="P1" s="14" t="s">
-        <v>1076</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>1077</v>
-      </c>
       <c r="R1" s="2" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>4</v>
@@ -4780,7 +4792,7 @@
         <v>10</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>11</v>
@@ -4810,7 +4822,7 @@
         <v>19</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AL1" s="2" t="s">
         <v>20</v>
@@ -4831,13 +4843,13 @@
         <v>25</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="AS1" s="2" t="s">
         <v>26</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="AU1" s="2" t="s">
         <v>27</v>
@@ -4846,19 +4858,19 @@
         <v>28</v>
       </c>
       <c r="AW1" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="AX1" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="AY1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="AZ1" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="BA1" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="2" spans="1:53">
@@ -4878,7 +4890,7 @@
         <v>27.72</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G2" s="15">
         <v>32.01</v>
@@ -4887,7 +4899,7 @@
         <v>24.3</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="J2" s="14">
         <v>28</v>
@@ -4900,7 +4912,7 @@
         <v>28.5</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="N2" s="14">
         <v>34</v>
@@ -4922,70 +4934,70 @@
         <v>35</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y2" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="Z2" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="AA2" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="AI2" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="AJ2" s="8">
         <v>0.33</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AL2" s="7">
         <v>0.40899999999999997</v>
       </c>
       <c r="AM2" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="AN2" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="AN2" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="AO2" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AQ2" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AS2" s="2" t="s">
         <v>63</v>
@@ -5000,16 +5012,16 @@
         <v>65</v>
       </c>
       <c r="AW2" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="AX2" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="AX2" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="AY2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="3" spans="1:53">
@@ -5047,11 +5059,11 @@
         <v>26</v>
       </c>
       <c r="L3" s="14">
-        <f t="shared" ref="L3:L50" si="0">(J3+K3)/2</f>
+        <f t="shared" ref="L3:L51" si="0">(J3+K3)/2</f>
         <v>26</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="N3" s="14">
         <v>29</v>
@@ -5060,7 +5072,7 @@
         <v>29</v>
       </c>
       <c r="P3" s="14">
-        <f t="shared" ref="P3:P50" si="1">(N3+O3)/2</f>
+        <f t="shared" ref="P3:P51" si="1">(N3+O3)/2</f>
         <v>29</v>
       </c>
       <c r="T3" s="2" t="s">
@@ -5085,7 +5097,7 @@
         <v>46</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>47</v>
@@ -5160,10 +5172,10 @@
         <v>65</v>
       </c>
       <c r="AZ3" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="4" spans="1:53">
@@ -5218,10 +5230,10 @@
         <v>26</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>72</v>
@@ -5245,7 +5257,7 @@
         <v>76</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB4" s="2" t="s">
         <v>77</v>
@@ -5320,10 +5332,10 @@
         <v>65</v>
       </c>
       <c r="AZ4" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5" spans="1:53">
@@ -5331,7 +5343,7 @@
         <v>89</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>90</v>
@@ -5376,10 +5388,10 @@
         <v>25</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R5" s="9" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>93</v>
@@ -5391,7 +5403,7 @@
         <v>35</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>44</v>
@@ -5403,7 +5415,7 @@
         <v>76</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>47</v>
@@ -5478,10 +5490,10 @@
         <v>65</v>
       </c>
       <c r="AZ5" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="6" spans="1:53">
@@ -5495,13 +5507,13 @@
         <v>111</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E6" s="16">
         <v>22.84</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G6" s="16">
         <v>26.27</v>
@@ -5510,7 +5522,7 @@
         <v>19.62</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="J6" s="14">
         <v>25</v>
@@ -5523,7 +5535,7 @@
         <v>25.5</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N6" s="14">
         <v>26</v>
@@ -5536,10 +5548,10 @@
         <v>26</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="U6" s="8">
         <v>0.8</v>
@@ -5548,70 +5560,70 @@
         <v>35</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC6" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="AD6" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="AD6" s="2" t="s">
+      <c r="AE6" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AF6" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="AF6" s="2" t="s">
+      <c r="AG6" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="AG6" s="2" t="s">
+      <c r="AH6" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="AH6" s="2" t="s">
+      <c r="AI6" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="AI6" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="AJ6" s="7">
         <v>0.32600000000000001</v>
       </c>
       <c r="AK6" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AL6" s="7">
         <v>0.44269999999999998</v>
       </c>
       <c r="AM6" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="AN6" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="AN6" s="7" t="s">
+      <c r="AO6" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="AO6" s="2" t="s">
+      <c r="AP6" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="AQ6" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR6" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AS6" s="2" t="s">
         <v>63</v>
@@ -5626,19 +5638,19 @@
         <v>65</v>
       </c>
       <c r="AW6" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="AX6" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="AX6" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="AY6" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ6" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7" spans="1:53">
@@ -5646,7 +5658,7 @@
         <v>112</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>113</v>
@@ -5693,7 +5705,7 @@
         <v>27</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>116</v>
@@ -5717,7 +5729,7 @@
         <v>46</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>47</v>
@@ -5792,10 +5804,10 @@
         <v>65</v>
       </c>
       <c r="AZ7" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="8" spans="1:53">
@@ -5837,7 +5849,7 @@
         <v>25.5</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="N8" s="14">
         <v>27</v>
@@ -5850,7 +5862,7 @@
         <v>28</v>
       </c>
       <c r="R8" s="9" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>138</v>
@@ -5874,7 +5886,7 @@
         <v>46</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB8" s="2" t="s">
         <v>47</v>
@@ -5949,10 +5961,10 @@
         <v>65</v>
       </c>
       <c r="AZ8" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA8" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="9" spans="1:53">
@@ -5986,7 +5998,7 @@
         <v>32.5</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="N9" s="14">
         <v>44</v>
@@ -6020,7 +6032,7 @@
         <v>46</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>47</v>
@@ -6095,10 +6107,10 @@
         <v>65</v>
       </c>
       <c r="AZ9" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA9" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" spans="1:53">
@@ -6118,7 +6130,7 @@
         <v>29.88</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G10" s="15">
         <v>37.450000000000003</v>
@@ -6140,7 +6152,7 @@
         <v>28.5</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="N10" s="14">
         <v>35</v>
@@ -6174,7 +6186,7 @@
         <v>46</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB10" s="2" t="s">
         <v>47</v>
@@ -6249,10 +6261,10 @@
         <v>65</v>
       </c>
       <c r="AZ10" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA10" s="2" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="11" spans="1:53">
@@ -6260,7 +6272,7 @@
         <v>202</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>203</v>
@@ -6294,7 +6306,7 @@
         <v>27</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="N11" s="14">
         <v>26</v>
@@ -6307,7 +6319,7 @@
         <v>27</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>205</v>
@@ -6331,7 +6343,7 @@
         <v>46</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>47</v>
@@ -6406,10 +6418,10 @@
         <v>65</v>
       </c>
       <c r="AZ11" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA11" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="12" spans="1:53" ht="16">
@@ -6423,13 +6435,13 @@
         <v>220</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E12" s="13">
         <v>24.17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G12" s="13">
         <v>26.76</v>
@@ -6438,7 +6450,7 @@
         <v>21.03</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="J12" s="14">
         <v>25</v>
@@ -6451,7 +6463,7 @@
         <v>25.5</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="N12" s="14">
         <v>27</v>
@@ -6464,7 +6476,7 @@
         <v>27.5</v>
       </c>
       <c r="R12" s="9" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="U12" s="8">
         <v>0.8</v>
@@ -6473,76 +6485,76 @@
         <v>35</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Z12" s="10" t="s">
         <v>46</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB12" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC12" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="AD12" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="AD12" s="2" t="s">
+      <c r="AE12" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="AE12" s="2" t="s">
+      <c r="AF12" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="AF12" s="2" t="s">
+      <c r="AG12" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="AG12" s="2" t="s">
+      <c r="AH12" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="AH12" s="2" t="s">
+      <c r="AI12" s="2" t="s">
         <v>588</v>
-      </c>
-      <c r="AI12" s="2" t="s">
-        <v>589</v>
       </c>
       <c r="AJ12" s="7">
         <v>0.31859999999999999</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AL12" s="7">
         <v>0.47989999999999999</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN12" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="AO12" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="AO12" s="2" t="s">
+      <c r="AP12" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="AP12" s="1" t="s">
-        <v>593</v>
       </c>
       <c r="AQ12" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR12" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AS12" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT12" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AU12" s="2" t="s">
         <v>65</v>
@@ -6551,24 +6563,24 @@
         <v>65</v>
       </c>
       <c r="AW12" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="AX12" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="AX12" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="AY12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ12" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA12" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="13" spans="1:53">
       <c r="A13" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>221</v>
@@ -6605,7 +6617,7 @@
         <v>31</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="N13" s="14">
         <v>38</v>
@@ -6618,7 +6630,7 @@
         <v>40</v>
       </c>
       <c r="R13" s="9" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>225</v>
@@ -6642,7 +6654,7 @@
         <v>76</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB13" s="2" t="s">
         <v>47</v>
@@ -6717,15 +6729,15 @@
         <v>65</v>
       </c>
       <c r="AZ13" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA13" s="9" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="14" spans="1:53" ht="16">
       <c r="A14" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>239</v>
@@ -6773,7 +6785,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>243</v>
@@ -6797,7 +6809,7 @@
         <v>46</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>47</v>
@@ -6872,30 +6884,30 @@
         <v>65</v>
       </c>
       <c r="AZ14" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA14" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="15" spans="1:53" ht="16">
       <c r="A15" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>786</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E15" s="15">
         <v>25.24</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G15" s="15">
         <v>30.14</v>
@@ -6904,7 +6916,7 @@
         <v>21.86</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J15" s="14">
         <v>28</v>
@@ -6917,7 +6929,7 @@
         <v>30.5</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="N15" s="14">
         <v>35</v>
@@ -6930,7 +6942,7 @@
         <v>37.5</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>42</v>
@@ -6939,99 +6951,99 @@
         <v>35</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC15" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="AD15" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="AD15" s="2" t="s">
+      <c r="AE15" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="AE15" s="2" t="s">
+      <c r="AF15" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="AF15" s="2" t="s">
+      <c r="AG15" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="AH15" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="AG15" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="AH15" s="2" t="s">
+      <c r="AI15" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="AI15" s="2" t="s">
+      <c r="AJ15" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="AJ15" s="2" t="s">
+      <c r="AK15" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="AK15" s="2" t="s">
-        <v>840</v>
       </c>
       <c r="AL15" s="7">
         <v>0.4743</v>
       </c>
       <c r="AM15" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN15" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="AO15" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP15" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AQ15" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR15" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AS15" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT15" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AV15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AW15" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="AX15" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AY15" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ15" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA15" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16" spans="1:53">
       <c r="A16" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>284</v>
@@ -7040,14 +7052,14 @@
         <v>285</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="17"/>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="J16" s="14">
         <v>35</v>
@@ -7060,7 +7072,7 @@
         <v>36.5</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="N16" s="14">
         <v>38</v>
@@ -7073,7 +7085,7 @@
         <v>40.5</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="U16" s="2" t="s">
         <v>42</v>
@@ -7082,76 +7094,76 @@
         <v>35</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="X16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y16" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Z16" s="10" t="s">
         <v>46</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB16" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC16" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="AD16" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="AD16" s="2" t="s">
+      <c r="AE16" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="AE16" s="2" t="s">
+      <c r="AF16" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="AF16" s="2" t="s">
+      <c r="AG16" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="AG16" s="2" t="s">
+      <c r="AH16" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="AH16" s="2" t="s">
+      <c r="AI16" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="AI16" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="AJ16" s="7">
         <v>0.33800000000000002</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AL16" s="7">
         <v>0.45529999999999998</v>
       </c>
       <c r="AM16" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="AN16" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="AN16" s="7" t="s">
+      <c r="AO16" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="AO16" s="2" t="s">
+      <c r="AP16" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="AP16" s="1" t="s">
-        <v>614</v>
       </c>
       <c r="AQ16" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR16" s="2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AS16" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT16" s="2" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AU16" s="2" t="s">
         <v>65</v>
@@ -7160,19 +7172,19 @@
         <v>65</v>
       </c>
       <c r="AW16" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="AX16" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="AX16" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="AY16" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ16" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA16" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="17" spans="1:53">
@@ -7183,14 +7195,14 @@
         <v>286</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>287</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>288</v>
       </c>
       <c r="E17" s="15"/>
       <c r="F17" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G17" s="15">
         <v>28.96</v>
@@ -7225,7 +7237,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>157</v>
@@ -7237,70 +7249,70 @@
         <v>35</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="X17" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y17" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC17" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD17" s="2" t="s">
         <v>269</v>
       </c>
       <c r="AE17" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="AF17" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AF17" s="3" t="s">
+      <c r="AG17" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AG17" s="2" t="s">
+      <c r="AH17" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AH17" s="2" t="s">
+      <c r="AI17" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="AI17" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="AJ17" s="2" t="s">
         <v>167</v>
       </c>
       <c r="AK17" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="AL17" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="AL17" s="2" t="s">
+      <c r="AM17" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AM17" s="2" t="s">
+      <c r="AN17" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="AN17" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="AO17" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP17" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AQ17" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR17" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AS17" s="2" t="s">
         <v>63</v>
@@ -7315,39 +7327,39 @@
         <v>65</v>
       </c>
       <c r="AW17" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="AX17" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="AX17" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="AY17" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ17" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA17" s="9" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:53">
       <c r="A18" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="E18" s="15">
         <v>26.84</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G18" s="15">
         <v>34.33</v>
@@ -7369,7 +7381,7 @@
         <v>27</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="N18" s="14">
         <v>33</v>
@@ -7382,7 +7394,7 @@
         <v>34.5</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>42</v>
@@ -7397,64 +7409,64 @@
         <v>44</v>
       </c>
       <c r="Y18" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Z18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB18" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC18" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD18" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AD18" s="2" t="s">
+      <c r="AE18" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AE18" s="2" t="s">
+      <c r="AF18" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AF18" s="2" t="s">
+      <c r="AG18" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="AG18" s="2" t="s">
+      <c r="AH18" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="AH18" s="2" t="s">
+      <c r="AI18" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="AI18" s="2" t="s">
+      <c r="AJ18" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="AJ18" s="2" t="s">
+      <c r="AK18" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="AK18" s="2" t="s">
+      <c r="AL18" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="AL18" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="AM18" s="2" t="s">
         <v>256</v>
       </c>
       <c r="AN18" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AO18" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP18" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AQ18" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR18" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AS18" s="2" t="s">
         <v>63</v>
@@ -7469,33 +7481,33 @@
         <v>65</v>
       </c>
       <c r="AW18" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AX18" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="AX18" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="AY18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ18" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA18" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="19" spans="1:53">
       <c r="A19" s="1" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>363</v>
-      </c>
       <c r="D19" s="9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E19" s="16">
         <v>26.4</v>
@@ -7510,7 +7522,7 @@
         <v>22.34</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="J19" s="14">
         <v>27</v>
@@ -7523,7 +7535,7 @@
         <v>28</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="N19" s="14">
         <v>27</v>
@@ -7536,13 +7548,13 @@
         <v>28</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R19" s="9" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>42</v>
@@ -7551,76 +7563,76 @@
         <v>35</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y19" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="Z19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC19" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="AE19" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="AD19" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="AE19" s="2" t="s">
+      <c r="AF19" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="AF19" s="2" t="s">
+      <c r="AG19" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="AG19" s="2" t="s">
+      <c r="AH19" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="AH19" s="2" t="s">
+      <c r="AI19" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="AI19" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="AJ19" s="7">
         <v>0.33500000000000002</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AL19" s="7">
         <v>0.59850000000000003</v>
       </c>
       <c r="AM19" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN19" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AP19" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AQ19" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR19" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AS19" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT19" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AU19" s="2" t="s">
         <v>65</v>
@@ -7629,33 +7641,33 @@
         <v>65</v>
       </c>
       <c r="AW19" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="AX19" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="AX19" s="2" t="s">
+      <c r="AY19" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="AY19" s="2" t="s">
-        <v>765</v>
-      </c>
       <c r="AZ19" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA19" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="20" spans="1:53">
       <c r="A20" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="E20" s="15">
         <v>23.36</v>
@@ -7670,7 +7682,7 @@
         <v>19.899999999999999</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J20" s="14">
         <v>24</v>
@@ -7683,7 +7695,7 @@
         <v>25</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="N20" s="14">
         <v>26</v>
@@ -7696,10 +7708,10 @@
         <v>27</v>
       </c>
       <c r="R20" s="9" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="U20" s="2" t="s">
         <v>42</v>
@@ -7714,34 +7726,34 @@
         <v>44</v>
       </c>
       <c r="Y20" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Z20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB20" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC20" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="AD20" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="AD20" s="2" t="s">
+      <c r="AE20" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="AE20" s="2" t="s">
+      <c r="AF20" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="AF20" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="AG20" s="2" t="s">
         <v>51</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AI20" s="2" t="s">
         <v>80</v>
@@ -7750,16 +7762,16 @@
         <v>54</v>
       </c>
       <c r="AK20" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="AL20" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="AL20" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="AM20" s="2" t="s">
         <v>148</v>
       </c>
       <c r="AN20" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AO20" s="2" t="s">
         <v>85</v>
@@ -7777,7 +7789,7 @@
         <v>63</v>
       </c>
       <c r="AT20" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AU20" s="2" t="s">
         <v>65</v>
@@ -7786,7 +7798,7 @@
         <v>65</v>
       </c>
       <c r="AW20" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AX20" s="2" t="s">
         <v>67</v>
@@ -7795,24 +7807,24 @@
         <v>65</v>
       </c>
       <c r="AZ20" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA20" s="2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="21" spans="1:53">
       <c r="A21" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="D21" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="17">
@@ -7825,7 +7837,7 @@
         <v>22.7</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J21" s="14">
         <v>26</v>
@@ -7838,7 +7850,7 @@
         <v>28</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="N21" s="14">
         <v>26</v>
@@ -7851,7 +7863,7 @@
         <v>28</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="U21" s="2" t="s">
         <v>42</v>
@@ -7860,76 +7872,76 @@
         <v>35</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y21" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Z21" s="10" t="s">
         <v>46</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB21" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC21" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="AE21" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="AD21" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="AE21" s="2" t="s">
+      <c r="AF21" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="AF21" s="2" t="s">
+      <c r="AG21" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="AG21" s="2" t="s">
+      <c r="AH21" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="AH21" s="2" t="s">
+      <c r="AI21" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="AI21" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="AJ21" s="8">
         <v>0.34</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AL21" s="7">
         <v>0.44359999999999999</v>
       </c>
       <c r="AM21" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="AN21" s="2" t="s">
         <v>743</v>
-      </c>
-      <c r="AN21" s="2" t="s">
-        <v>744</v>
       </c>
       <c r="AO21" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP21" s="1" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AQ21" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR21" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AS21" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT21" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AU21" s="2" t="s">
         <v>65</v>
@@ -7938,33 +7950,33 @@
         <v>65</v>
       </c>
       <c r="AW21" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="AX21" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="AX21" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="AY21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ21" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA21" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="22" spans="1:53">
       <c r="A22" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E22" s="15">
         <v>24.96</v>
@@ -7979,7 +7991,7 @@
         <v>23.49</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J22" s="14">
         <v>28</v>
@@ -7992,7 +8004,7 @@
         <v>30</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="N22" s="14">
         <v>34</v>
@@ -8005,7 +8017,7 @@
         <v>35</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U22" s="2" t="s">
         <v>42</v>
@@ -8020,22 +8032,22 @@
         <v>44</v>
       </c>
       <c r="Y22" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Z22" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AA22" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB22" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="AC22" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="AC22" s="2" t="s">
+      <c r="AD22" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="AE22" s="2" t="s">
         <v>162</v>
@@ -8047,43 +8059,43 @@
         <v>164</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AI22" s="2" t="s">
         <v>211</v>
       </c>
       <c r="AJ22" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="AK22" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="AK22" s="2" t="s">
+      <c r="AL22" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="AL22" s="2" t="s">
+      <c r="AM22" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="AM22" s="2" t="s">
+      <c r="AN22" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="AN22" s="2" t="s">
+      <c r="AO22" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="AO22" s="2" t="s">
+      <c r="AP22" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="AP22" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="AQ22" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR22" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AS22" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT22" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AU22" s="2" t="s">
         <v>65</v>
@@ -8092,33 +8104,33 @@
         <v>65</v>
       </c>
       <c r="AW22" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="AX22" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="AX22" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="AY22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ22" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="BA22" s="9" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="23" spans="1:53">
       <c r="A23" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="D23" s="9" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="F23" s="4">
         <v>21.94</v>
@@ -8130,7 +8142,7 @@
         <v>19.66</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J23" s="14">
         <v>24</v>
@@ -8143,7 +8155,7 @@
         <v>25</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="N23" s="14">
         <v>24</v>
@@ -8156,16 +8168,16 @@
         <v>25</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="U23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="W23" s="2" t="s">
         <v>74</v>
@@ -8174,34 +8186,34 @@
         <v>44</v>
       </c>
       <c r="Y23" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Z23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="AA23" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC23" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="AE23" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="AD23" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="AE23" s="2" t="s">
+      <c r="AF23" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="AF23" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="AG23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AI23" s="2" t="s">
         <v>99</v>
@@ -8210,16 +8222,16 @@
         <v>126</v>
       </c>
       <c r="AK23" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="AL23" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="AL23" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="AM23" s="2" t="s">
         <v>148</v>
       </c>
       <c r="AN23" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO23" s="2" t="s">
         <v>85</v>
@@ -8231,13 +8243,13 @@
         <v>61</v>
       </c>
       <c r="AR23" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AS23" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT23" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AU23" s="2" t="s">
         <v>65</v>
@@ -8246,7 +8258,7 @@
         <v>65</v>
       </c>
       <c r="AW23" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AX23" s="2" t="s">
         <v>283</v>
@@ -8255,24 +8267,24 @@
         <v>65</v>
       </c>
       <c r="AZ23" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="BA23" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="24" spans="1:53">
       <c r="A24" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>420</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E24" s="16">
         <v>23.59</v>
@@ -8287,7 +8299,7 @@
         <v>20</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J24" s="14">
         <v>30</v>
@@ -8300,7 +8312,7 @@
         <v>30.5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="N24" s="14">
         <v>28</v>
@@ -8313,10 +8325,10 @@
         <v>28</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="U24" s="2" t="s">
         <v>42</v>
@@ -8325,76 +8337,76 @@
         <v>35</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="X24" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB24" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC24" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="AD24" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="AD24" s="2" t="s">
+      <c r="AE24" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="AE24" s="2" t="s">
+      <c r="AF24" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="AF24" s="2" t="s">
+      <c r="AG24" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="AH24" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="AG24" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="AH24" s="2" t="s">
+      <c r="AI24" s="2" t="s">
         <v>627</v>
-      </c>
-      <c r="AI24" s="2" t="s">
-        <v>628</v>
       </c>
       <c r="AJ24" s="8">
         <v>0.32</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AL24" s="7">
         <v>0.44209999999999999</v>
       </c>
       <c r="AM24" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN24" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AO24" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="AP24" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="AP24" s="1" t="s">
-        <v>593</v>
       </c>
       <c r="AQ24" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR24" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AS24" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT24" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AU24" s="2" t="s">
         <v>65</v>
@@ -8403,39 +8415,39 @@
         <v>65</v>
       </c>
       <c r="AW24" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="AX24" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="AX24" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="AY24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ24" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="BA24" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="25" spans="1:53">
       <c r="A25" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>788</v>
-      </c>
       <c r="C25" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E25" s="16">
         <v>24.76</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G25" s="16">
         <v>29.05</v>
@@ -8444,7 +8456,7 @@
         <v>21.81</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="J25" s="14">
         <v>29</v>
@@ -8457,7 +8469,7 @@
         <v>30</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="N25" s="14">
         <v>34</v>
@@ -8470,7 +8482,7 @@
         <v>36.5</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="U25" s="2" t="s">
         <v>42</v>
@@ -8479,114 +8491,114 @@
         <v>35</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="X25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB25" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC25" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="AD25" s="2" t="s">
         <v>817</v>
       </c>
-      <c r="AD25" s="2" t="s">
+      <c r="AE25" s="2" t="s">
         <v>818</v>
       </c>
-      <c r="AE25" s="2" t="s">
+      <c r="AF25" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="AF25" s="2" t="s">
+      <c r="AG25" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="AH25" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="AG25" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="AH25" s="2" t="s">
+      <c r="AI25" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="AI25" s="2" t="s">
-        <v>822</v>
       </c>
       <c r="AJ25" s="8">
         <v>0.32</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AL25" s="7">
         <v>0.55610000000000004</v>
       </c>
       <c r="AM25" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="AN25" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="AN25" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="AO25" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP25" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AQ25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR25" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AS25" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT25" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AV25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AW25" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AX25" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AY25" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ25" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA25" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="26" spans="1:53">
       <c r="A26" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>790</v>
-      </c>
       <c r="C26" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E26" s="16">
         <v>25.71</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G26" s="16">
         <v>31.03</v>
@@ -8595,7 +8607,7 @@
         <v>23.19</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J26" s="14">
         <v>27</v>
@@ -8608,7 +8620,7 @@
         <v>27</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="N26" s="14">
         <v>32</v>
@@ -8621,315 +8633,205 @@
         <v>33</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="U26" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V26" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="W26" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>802</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC26" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="AD26" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="AD26" s="2" t="s">
+      <c r="AE26" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="AG26" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="AH26" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="AE26" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="AF26" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="AH26" s="2" t="s">
+      <c r="AI26" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="AI26" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="AJ26" s="8">
         <v>0.32500000000000001</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AL26" s="7">
         <v>0.3347</v>
       </c>
       <c r="AM26" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AN26" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AO26" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP26" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AQ26" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR26" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="AS26" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT26" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AV26" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AW26" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="AX26" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="AY26" s="2" t="s">
         <v>811</v>
       </c>
-      <c r="AX26" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="AY26" s="2" t="s">
-        <v>812</v>
-      </c>
       <c r="AZ26" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="BA26" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="27" spans="1:53">
       <c r="A27" s="1" t="s">
-        <v>773</v>
+        <v>1102</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E27" s="15">
-        <v>26.45</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G27" s="15">
-        <v>28.89</v>
-      </c>
-      <c r="H27" s="15">
-        <v>22.46</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J27" s="14">
-        <v>26</v>
-      </c>
-      <c r="K27" s="14">
-        <v>28</v>
-      </c>
-      <c r="L27" s="14">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>1103</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="17" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G27" s="16">
+        <v>28.96</v>
+      </c>
+      <c r="H27" s="16">
+        <v>19.2</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>1064</v>
+        <v>1106</v>
       </c>
       <c r="N27" s="14">
-        <v>38</v>
+        <v>33.47</v>
       </c>
       <c r="O27" s="14">
-        <v>41</v>
+        <v>33.47</v>
       </c>
       <c r="P27" s="14">
-        <f t="shared" si="1"/>
-        <v>39.5</v>
-      </c>
-      <c r="R27" s="9" t="s">
-        <v>945</v>
-      </c>
-      <c r="U27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="X27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>268</v>
+        <v>33.47</v>
       </c>
       <c r="Z27" s="2" t="s">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="AB27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC27" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="AE27" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="AF27" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="AG27" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="AH27" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="AI27" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="AJ27" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="AK27" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="AL27" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="AM27" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="AN27" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="AO27" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP27" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="AQ27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AR27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="AS27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AT27" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="AU27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AW27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="AX27" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="AY27" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>767</v>
+      </c>
+      <c r="AJ27" s="8"/>
+      <c r="AL27" s="7"/>
       <c r="AZ27" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="BA27" s="2" t="s">
-        <v>1011</v>
+        <v>984</v>
       </c>
     </row>
     <row r="28" spans="1:53">
       <c r="A28" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>327</v>
+        <v>265</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>328</v>
+        <v>266</v>
       </c>
       <c r="E28" s="15">
-        <v>26.46</v>
-      </c>
-      <c r="F28" s="4">
-        <v>24.18</v>
+        <v>26.45</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>1086</v>
       </c>
       <c r="G28" s="15">
-        <v>29.57</v>
+        <v>28.89</v>
       </c>
       <c r="H28" s="15">
-        <v>21.5</v>
+        <v>22.46</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>329</v>
+        <v>115</v>
       </c>
       <c r="J28" s="14">
-        <v>30.5</v>
+        <v>26</v>
       </c>
       <c r="K28" s="14">
-        <v>30.5</v>
+        <v>28</v>
       </c>
       <c r="L28" s="14">
         <f t="shared" si="0"/>
-        <v>30.5</v>
+        <v>27</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>329</v>
+        <v>1062</v>
       </c>
       <c r="N28" s="14">
-        <v>30.5</v>
+        <v>38</v>
       </c>
       <c r="O28" s="14">
-        <v>30.5</v>
+        <v>41</v>
       </c>
       <c r="P28" s="14">
         <f t="shared" si="1"/>
-        <v>30.5</v>
+        <v>39.5</v>
       </c>
       <c r="R28" s="9" t="s">
-        <v>944</v>
-      </c>
-      <c r="T28" s="2" t="s">
-        <v>330</v>
+        <v>943</v>
       </c>
       <c r="U28" s="2" t="s">
         <v>42</v>
@@ -8938,70 +8840,70 @@
         <v>35</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="X28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>331</v>
+        <v>268</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>332</v>
+        <v>269</v>
       </c>
       <c r="AD28" s="2" t="s">
-        <v>332</v>
+        <v>270</v>
       </c>
       <c r="AE28" s="2" t="s">
-        <v>49</v>
+        <v>271</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="AG28" s="2" t="s">
-        <v>51</v>
+        <v>273</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>334</v>
+        <v>277</v>
       </c>
       <c r="AL28" s="2" t="s">
-        <v>335</v>
+        <v>278</v>
       </c>
       <c r="AM28" s="2" t="s">
-        <v>336</v>
+        <v>170</v>
       </c>
       <c r="AN28" s="2" t="s">
-        <v>337</v>
+        <v>279</v>
       </c>
       <c r="AO28" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP28" s="1" t="s">
-        <v>338</v>
+        <v>280</v>
       </c>
       <c r="AQ28" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR28" s="2" t="s">
-        <v>339</v>
+        <v>281</v>
       </c>
       <c r="AS28" s="2" t="s">
         <v>63</v>
@@ -9016,66 +8918,77 @@
         <v>65</v>
       </c>
       <c r="AW28" s="2" t="s">
-        <v>340</v>
+        <v>282</v>
       </c>
       <c r="AX28" s="2" t="s">
-        <v>341</v>
+        <v>283</v>
       </c>
       <c r="AY28" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ28" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA28" s="2" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="29" spans="1:53">
       <c r="A29" s="1" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>502</v>
+        <v>325</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>503</v>
+        <v>326</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+        <v>327</v>
+      </c>
+      <c r="E29" s="15">
+        <v>26.46</v>
+      </c>
+      <c r="F29" s="4">
+        <v>24.18</v>
+      </c>
+      <c r="G29" s="15">
+        <v>29.57</v>
+      </c>
+      <c r="H29" s="15">
+        <v>21.5</v>
+      </c>
       <c r="I29" s="2" t="s">
-        <v>505</v>
+        <v>328</v>
       </c>
       <c r="J29" s="14">
-        <v>35</v>
+        <v>30.5</v>
       </c>
       <c r="K29" s="14">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="L29" s="14">
         <f t="shared" si="0"/>
-        <v>36.5</v>
+        <v>30.5</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>1065</v>
+        <v>328</v>
       </c>
       <c r="N29" s="14">
-        <v>45</v>
+        <v>30.5</v>
       </c>
       <c r="O29" s="14">
-        <v>48</v>
+        <v>30.5</v>
       </c>
       <c r="P29" s="14">
         <f t="shared" si="1"/>
-        <v>46.5</v>
+        <v>30.5</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>942</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>506</v>
+        <v>329</v>
       </c>
       <c r="U29" s="2" t="s">
         <v>42</v>
@@ -9083,29 +8996,29 @@
       <c r="V29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="5" t="s">
-        <v>507</v>
+      <c r="W29" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="X29" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y29" s="2" t="s">
-        <v>508</v>
+        <v>330</v>
       </c>
       <c r="Z29" s="2" t="s">
         <v>46</v>
       </c>
       <c r="AA29" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>509</v>
+        <v>331</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>510</v>
+        <v>331</v>
       </c>
       <c r="AE29" s="2" t="s">
         <v>49</v>
@@ -9117,37 +9030,37 @@
         <v>51</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>511</v>
+        <v>332</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>512</v>
+        <v>80</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>54</v>
+        <v>253</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>513</v>
+        <v>333</v>
       </c>
       <c r="AL29" s="2" t="s">
-        <v>514</v>
+        <v>334</v>
       </c>
       <c r="AM29" s="2" t="s">
-        <v>515</v>
+        <v>335</v>
       </c>
       <c r="AN29" s="2" t="s">
-        <v>516</v>
+        <v>336</v>
       </c>
       <c r="AO29" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP29" s="1" t="s">
-        <v>517</v>
+        <v>337</v>
       </c>
       <c r="AQ29" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR29" s="2" t="s">
-        <v>518</v>
+        <v>338</v>
       </c>
       <c r="AS29" s="2" t="s">
         <v>63</v>
@@ -9162,77 +9075,66 @@
         <v>65</v>
       </c>
       <c r="AW29" s="2" t="s">
-        <v>519</v>
+        <v>339</v>
       </c>
       <c r="AX29" s="2" t="s">
-        <v>67</v>
+        <v>340</v>
       </c>
       <c r="AY29" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ29" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA29" s="2" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="30" spans="1:53">
       <c r="A30" s="1" t="s">
-        <v>438</v>
+        <v>778</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="E30" s="15">
-        <v>21.19</v>
-      </c>
-      <c r="F30" s="4">
-        <v>32.74</v>
-      </c>
-      <c r="G30" s="15">
-        <v>48.58</v>
-      </c>
-      <c r="H30" s="15">
-        <v>19.559999999999999</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
       <c r="I30" s="2" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="J30" s="14">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="K30" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L30" s="14">
         <f t="shared" si="0"/>
-        <v>29.5</v>
+        <v>36.5</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="N30" s="14">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="O30" s="14">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="P30" s="14">
         <f t="shared" si="1"/>
-        <v>24.5</v>
-      </c>
-      <c r="Q30" s="14" t="s">
-        <v>1079</v>
+        <v>46.5</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="U30" s="2" t="s">
         <v>42</v>
@@ -9241,70 +9143,70 @@
         <v>35</v>
       </c>
       <c r="W30" s="5" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="X30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y30" s="2" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="Z30" s="2" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="AA30" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB30" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="AD30" s="2" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="AE30" s="2" t="s">
-        <v>469</v>
+        <v>49</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>470</v>
+        <v>50</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>471</v>
+        <v>51</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>473</v>
+        <v>511</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>474</v>
+        <v>54</v>
       </c>
       <c r="AK30" s="2" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="AL30" s="2" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="AM30" s="2" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="AN30" s="2" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="AO30" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP30" s="1" t="s">
-        <v>215</v>
+        <v>516</v>
       </c>
       <c r="AQ30" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR30" s="2" t="s">
-        <v>479</v>
+        <v>517</v>
       </c>
       <c r="AS30" s="2" t="s">
         <v>63</v>
@@ -9319,74 +9221,77 @@
         <v>65</v>
       </c>
       <c r="AW30" s="2" t="s">
-        <v>480</v>
+        <v>518</v>
       </c>
       <c r="AX30" s="2" t="s">
-        <v>262</v>
+        <v>67</v>
       </c>
       <c r="AY30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ30" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA30" s="2" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="31" spans="1:53">
       <c r="A31" s="1" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>667</v>
-      </c>
-      <c r="E31" s="16">
-        <v>26.59</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G31" s="16">
-        <v>31.65</v>
-      </c>
-      <c r="H31" s="16">
-        <v>24.01</v>
+        <v>460</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E31" s="15">
+        <v>21.19</v>
+      </c>
+      <c r="F31" s="4">
+        <v>32.74</v>
+      </c>
+      <c r="G31" s="15">
+        <v>48.58</v>
+      </c>
+      <c r="H31" s="15">
+        <v>19.559999999999999</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>668</v>
+        <v>462</v>
       </c>
       <c r="J31" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K31" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L31" s="14">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>29.5</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>911</v>
+        <v>1064</v>
       </c>
       <c r="N31" s="14">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O31" s="14">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P31" s="14">
         <f t="shared" si="1"/>
-        <v>33.5</v>
+        <v>24.5</v>
+      </c>
+      <c r="Q31" s="14" t="s">
+        <v>1077</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>669</v>
+        <v>463</v>
       </c>
       <c r="U31" s="2" t="s">
         <v>42</v>
@@ -9394,77 +9299,77 @@
       <c r="V31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="W31" s="2" t="s">
-        <v>670</v>
+      <c r="W31" s="5" t="s">
+        <v>464</v>
       </c>
       <c r="X31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y31" s="2" t="s">
-        <v>671</v>
+        <v>465</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>403</v>
+        <v>76</v>
       </c>
       <c r="AA31" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB31" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>672</v>
+        <v>466</v>
       </c>
       <c r="AD31" s="2" t="s">
-        <v>673</v>
+        <v>467</v>
       </c>
       <c r="AE31" s="2" t="s">
-        <v>674</v>
+        <v>468</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>675</v>
+        <v>469</v>
       </c>
       <c r="AG31" s="2" t="s">
-        <v>549</v>
+        <v>470</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>676</v>
+        <v>471</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="AJ31" s="8">
-        <v>0.32</v>
+        <v>472</v>
+      </c>
+      <c r="AJ31" s="2" t="s">
+        <v>473</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="AL31" s="7">
-        <v>0.46450000000000002</v>
+        <v>474</v>
+      </c>
+      <c r="AL31" s="2" t="s">
+        <v>475</v>
       </c>
       <c r="AM31" s="2" t="s">
-        <v>553</v>
+        <v>476</v>
       </c>
       <c r="AN31" s="2" t="s">
-        <v>678</v>
+        <v>477</v>
       </c>
       <c r="AO31" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP31" s="1" t="s">
-        <v>593</v>
+        <v>215</v>
       </c>
       <c r="AQ31" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR31" s="2" t="s">
-        <v>679</v>
+        <v>478</v>
       </c>
       <c r="AS31" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT31" s="2" t="s">
-        <v>595</v>
+        <v>260</v>
       </c>
       <c r="AU31" s="2" t="s">
         <v>65</v>
@@ -9473,77 +9378,74 @@
         <v>65</v>
       </c>
       <c r="AW31" s="2" t="s">
-        <v>680</v>
+        <v>479</v>
       </c>
       <c r="AX31" s="2" t="s">
-        <v>681</v>
+        <v>262</v>
       </c>
       <c r="AY31" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ31" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA31" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="32" spans="1:53">
       <c r="A32" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="E32" s="15">
-        <v>25.73</v>
-      </c>
-      <c r="F32" s="4">
-        <v>23.14</v>
-      </c>
-      <c r="G32" s="15">
-        <v>31.69</v>
-      </c>
-      <c r="H32" s="15">
-        <v>19.95</v>
+        <v>457</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="E32" s="16">
+        <v>26.59</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G32" s="16">
+        <v>31.65</v>
+      </c>
+      <c r="H32" s="16">
+        <v>24.01</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>242</v>
+        <v>667</v>
       </c>
       <c r="J32" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K32" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L32" s="14">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>1067</v>
+        <v>910</v>
       </c>
       <c r="N32" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O32" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P32" s="14">
         <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="R32" s="9" t="s">
-        <v>943</v>
+        <v>33.5</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="U32" s="2" t="s">
         <v>42</v>
@@ -9552,76 +9454,76 @@
         <v>35</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>74</v>
+        <v>669</v>
       </c>
       <c r="X32" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>489</v>
+        <v>670</v>
       </c>
       <c r="Z32" s="2" t="s">
-        <v>76</v>
+        <v>402</v>
       </c>
       <c r="AA32" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>490</v>
+        <v>671</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>491</v>
+        <v>672</v>
       </c>
       <c r="AE32" s="2" t="s">
-        <v>492</v>
+        <v>673</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>493</v>
+        <v>674</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>51</v>
+        <v>548</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>494</v>
+        <v>675</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="AJ32" s="2" t="s">
-        <v>81</v>
+        <v>644</v>
+      </c>
+      <c r="AJ32" s="8">
+        <v>0.32</v>
       </c>
       <c r="AK32" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="AL32" s="2" t="s">
-        <v>497</v>
+        <v>676</v>
+      </c>
+      <c r="AL32" s="7">
+        <v>0.46450000000000002</v>
       </c>
       <c r="AM32" s="2" t="s">
-        <v>195</v>
+        <v>552</v>
       </c>
       <c r="AN32" s="2" t="s">
-        <v>498</v>
+        <v>677</v>
       </c>
       <c r="AO32" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AP32" s="1" t="s">
-        <v>499</v>
+        <v>592</v>
       </c>
       <c r="AQ32" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR32" s="2" t="s">
-        <v>453</v>
+        <v>678</v>
       </c>
       <c r="AS32" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT32" s="2" t="s">
-        <v>359</v>
+        <v>594</v>
       </c>
       <c r="AU32" s="2" t="s">
         <v>65</v>
@@ -9630,74 +9532,77 @@
         <v>65</v>
       </c>
       <c r="AW32" s="2" t="s">
-        <v>500</v>
+        <v>679</v>
       </c>
       <c r="AX32" s="2" t="s">
-        <v>67</v>
+        <v>680</v>
       </c>
       <c r="AY32" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ32" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="BA32" s="9" t="s">
-        <v>1016</v>
+        <v>984</v>
+      </c>
+      <c r="BA32" s="2" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="33" spans="1:53">
       <c r="A33" s="1" t="s">
-        <v>780</v>
+        <v>458</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>770</v>
+        <v>484</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>425</v>
+        <v>485</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>426</v>
+        <v>486</v>
       </c>
       <c r="E33" s="15">
-        <v>34.08</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>1090</v>
+        <v>25.73</v>
+      </c>
+      <c r="F33" s="4">
+        <v>23.14</v>
       </c>
       <c r="G33" s="15">
-        <v>41.77</v>
+        <v>31.69</v>
       </c>
       <c r="H33" s="15">
-        <v>22.76</v>
+        <v>19.95</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>427</v>
+        <v>242</v>
       </c>
       <c r="J33" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K33" s="14">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L33" s="14">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>28</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>1052</v>
+        <v>1065</v>
       </c>
       <c r="N33" s="14">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O33" s="14">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="1"/>
-        <v>46.5</v>
+        <v>31</v>
+      </c>
+      <c r="R33" s="9" t="s">
+        <v>941</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>428</v>
+        <v>487</v>
       </c>
       <c r="U33" s="2" t="s">
         <v>42</v>
@@ -9706,76 +9611,76 @@
         <v>35</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>429</v>
+        <v>74</v>
       </c>
       <c r="X33" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>430</v>
+        <v>488</v>
       </c>
       <c r="Z33" s="2" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="AA33" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC33" s="2" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>432</v>
+        <v>490</v>
       </c>
       <c r="AE33" s="2" t="s">
-        <v>162</v>
+        <v>491</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>163</v>
+        <v>492</v>
       </c>
       <c r="AG33" s="2" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>165</v>
+        <v>493</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>211</v>
+        <v>494</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AK33" s="2" t="s">
-        <v>433</v>
+        <v>495</v>
       </c>
       <c r="AL33" s="2" t="s">
-        <v>434</v>
+        <v>496</v>
       </c>
       <c r="AM33" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="AN33" s="2" t="s">
-        <v>435</v>
+        <v>497</v>
       </c>
       <c r="AO33" s="2" t="s">
-        <v>377</v>
+        <v>85</v>
       </c>
       <c r="AP33" s="1" t="s">
-        <v>215</v>
+        <v>498</v>
       </c>
       <c r="AQ33" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR33" s="2" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="AS33" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT33" s="2" t="s">
-        <v>595</v>
+        <v>358</v>
       </c>
       <c r="AU33" s="2" t="s">
         <v>65</v>
@@ -9784,72 +9689,74 @@
         <v>65</v>
       </c>
       <c r="AW33" s="2" t="s">
-        <v>437</v>
+        <v>499</v>
       </c>
       <c r="AX33" s="2" t="s">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="AY33" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ33" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="BA33" s="2" t="s">
-        <v>1017</v>
+        <v>984</v>
+      </c>
+      <c r="BA33" s="9" t="s">
+        <v>1014</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="21">
+    <row r="34" spans="1:53">
       <c r="A34" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>482</v>
+        <v>779</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>769</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="17">
-        <v>24.99</v>
-      </c>
-      <c r="G34" s="16">
-        <v>27.76</v>
-      </c>
-      <c r="H34" s="16">
-        <v>22.52</v>
+        <v>424</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E34" s="15">
+        <v>34.08</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G34" s="15">
+        <v>41.77</v>
+      </c>
+      <c r="H34" s="15">
+        <v>22.76</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>685</v>
+        <v>426</v>
       </c>
       <c r="J34" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K34" s="14">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L34" s="14">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>35.5</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>685</v>
+        <v>1050</v>
       </c>
       <c r="N34" s="14">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="O34" s="14">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="P34" s="14">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>46.5</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>686</v>
+        <v>427</v>
       </c>
       <c r="U34" s="2" t="s">
         <v>42</v>
@@ -9858,76 +9765,76 @@
         <v>35</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>687</v>
+        <v>428</v>
       </c>
       <c r="X34" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>688</v>
+        <v>429</v>
       </c>
       <c r="Z34" s="2" t="s">
-        <v>403</v>
+        <v>46</v>
       </c>
       <c r="AA34" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="AD34" s="11" t="s">
-        <v>689</v>
+        <v>430</v>
+      </c>
+      <c r="AD34" s="2" t="s">
+        <v>431</v>
       </c>
       <c r="AE34" s="2" t="s">
-        <v>690</v>
+        <v>162</v>
       </c>
       <c r="AF34" s="2" t="s">
-        <v>691</v>
+        <v>163</v>
       </c>
       <c r="AG34" s="2" t="s">
-        <v>692</v>
+        <v>164</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>693</v>
+        <v>165</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="AJ34" s="8">
-        <v>0.32</v>
+        <v>211</v>
+      </c>
+      <c r="AJ34" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="AK34" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="AL34" s="7">
-        <v>0.4622</v>
+        <v>432</v>
+      </c>
+      <c r="AL34" s="2" t="s">
+        <v>433</v>
       </c>
       <c r="AM34" s="2" t="s">
-        <v>553</v>
+        <v>170</v>
       </c>
       <c r="AN34" s="2" t="s">
-        <v>682</v>
+        <v>434</v>
       </c>
       <c r="AO34" s="2" t="s">
-        <v>85</v>
+        <v>376</v>
       </c>
       <c r="AP34" s="1" t="s">
-        <v>696</v>
+        <v>215</v>
       </c>
       <c r="AQ34" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR34" s="2" t="s">
-        <v>697</v>
+        <v>435</v>
       </c>
       <c r="AS34" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT34" s="2" t="s">
-        <v>683</v>
+        <v>594</v>
       </c>
       <c r="AU34" s="2" t="s">
         <v>65</v>
@@ -9936,150 +9843,150 @@
         <v>65</v>
       </c>
       <c r="AW34" s="2" t="s">
-        <v>698</v>
+        <v>436</v>
       </c>
       <c r="AX34" s="2" t="s">
-        <v>699</v>
+        <v>177</v>
       </c>
       <c r="AY34" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ34" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA34" s="2" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
-    <row r="35" spans="1:53">
+    <row r="35" spans="1:53" ht="21">
       <c r="A35" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>423</v>
+        <v>481</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="E35" s="16"/>
       <c r="F35" s="17">
-        <v>26.39</v>
+        <v>24.99</v>
       </c>
       <c r="G35" s="16">
-        <v>29.56</v>
+        <v>27.76</v>
       </c>
       <c r="H35" s="16">
-        <v>23.12</v>
+        <v>22.52</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="J35" s="14">
         <v>30</v>
       </c>
       <c r="K35" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L35" s="14">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="N35" s="14">
         <v>30</v>
       </c>
       <c r="O35" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P35" s="14">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="U35" s="8">
-        <v>0.75</v>
+        <v>685</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>35</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>656</v>
+        <v>686</v>
       </c>
       <c r="X35" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>657</v>
+        <v>687</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA35" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB35" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC35" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="AD35" s="2" t="s">
-        <v>640</v>
+        <v>688</v>
+      </c>
+      <c r="AD35" s="11" t="s">
+        <v>688</v>
       </c>
       <c r="AE35" s="2" t="s">
-        <v>641</v>
+        <v>689</v>
       </c>
       <c r="AF35" s="2" t="s">
-        <v>642</v>
+        <v>690</v>
       </c>
       <c r="AG35" s="2" t="s">
-        <v>643</v>
+        <v>691</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>644</v>
+        <v>692</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="AJ35" s="7">
-        <v>0.33</v>
+        <v>693</v>
+      </c>
+      <c r="AJ35" s="8">
+        <v>0.32</v>
       </c>
       <c r="AK35" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="AL35" s="7" t="s">
-        <v>660</v>
+        <v>694</v>
+      </c>
+      <c r="AL35" s="7">
+        <v>0.4622</v>
       </c>
       <c r="AM35" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="AN35" s="7" t="s">
-        <v>662</v>
+        <v>552</v>
+      </c>
+      <c r="AN35" s="2" t="s">
+        <v>681</v>
       </c>
       <c r="AO35" s="2" t="s">
-        <v>649</v>
+        <v>85</v>
       </c>
       <c r="AP35" s="1" t="s">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="AQ35" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR35" s="2" t="s">
-        <v>664</v>
+        <v>696</v>
       </c>
       <c r="AS35" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT35" s="2" t="s">
-        <v>595</v>
+        <v>682</v>
       </c>
       <c r="AU35" s="2" t="s">
         <v>65</v>
@@ -10088,152 +9995,150 @@
         <v>65</v>
       </c>
       <c r="AW35" s="2" t="s">
-        <v>665</v>
+        <v>697</v>
       </c>
       <c r="AX35" s="2" t="s">
-        <v>666</v>
+        <v>698</v>
       </c>
       <c r="AY35" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ35" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA35" s="2" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="16">
+    <row r="36" spans="1:53">
       <c r="A36" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>421</v>
+        <v>483</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>422</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="E36" s="16">
-        <v>30.02</v>
-      </c>
+        <v>652</v>
+      </c>
+      <c r="E36" s="16"/>
       <c r="F36" s="17">
-        <v>29.48</v>
+        <v>26.39</v>
       </c>
       <c r="G36" s="16">
+        <v>29.56</v>
+      </c>
+      <c r="H36" s="16">
+        <v>23.12</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="J36" s="14">
+        <v>30</v>
+      </c>
+      <c r="K36" s="14">
         <v>32</v>
-      </c>
-      <c r="H36" s="16">
-        <v>25.65</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="J36" s="14">
-        <v>33</v>
-      </c>
-      <c r="K36" s="14">
-        <v>38</v>
       </c>
       <c r="L36" s="14">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>31</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="N36" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O36" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="P36" s="14">
         <f t="shared" si="1"/>
-        <v>35.5</v>
+        <v>31</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>42</v>
+        <v>654</v>
+      </c>
+      <c r="U36" s="8">
+        <v>0.75</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="X36" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="Z36" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA36" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC36" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="AD36" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="AD36" s="2" t="s">
+      <c r="AE36" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="AE36" s="2" t="s">
+      <c r="AF36" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="AF36" s="2" t="s">
+      <c r="AG36" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="AG36" s="2" t="s">
+      <c r="AH36" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="AH36" s="2" t="s">
+      <c r="AI36" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="AI36" s="2" t="s">
-        <v>645</v>
-      </c>
       <c r="AJ36" s="7">
-        <v>0.3327</v>
+        <v>0.33</v>
       </c>
       <c r="AK36" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="AL36" s="7">
-        <v>0.38300000000000001</v>
+        <v>658</v>
+      </c>
+      <c r="AL36" s="7" t="s">
+        <v>659</v>
       </c>
       <c r="AM36" s="2" t="s">
-        <v>647</v>
+        <v>660</v>
       </c>
       <c r="AN36" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="AO36" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="AO36" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="AP36" s="1" t="s">
-        <v>593</v>
+        <v>662</v>
       </c>
       <c r="AQ36" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR36" s="2" t="s">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="AS36" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT36" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AU36" s="2" t="s">
         <v>65</v>
@@ -10242,74 +10147,74 @@
         <v>65</v>
       </c>
       <c r="AW36" s="2" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="AX36" s="2" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="AY36" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ36" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA36" s="2" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
     </row>
-    <row r="37" spans="1:53">
+    <row r="37" spans="1:53" ht="16">
       <c r="A37" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>439</v>
+        <v>500</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>420</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="E37" s="15">
-        <v>26.33</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G37" s="15">
-        <v>28.67</v>
-      </c>
-      <c r="H37" s="15">
-        <v>21.01</v>
+        <v>421</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="E37" s="16">
+        <v>30.02</v>
+      </c>
+      <c r="F37" s="17">
+        <v>29.48</v>
+      </c>
+      <c r="G37" s="16">
+        <v>32</v>
+      </c>
+      <c r="H37" s="16">
+        <v>25.65</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>442</v>
+        <v>634</v>
       </c>
       <c r="J37" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K37" s="14">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="L37" s="14">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>35.5</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>1067</v>
+        <v>634</v>
       </c>
       <c r="N37" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O37" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="P37" s="14">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>35.5</v>
       </c>
       <c r="T37" s="2" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="U37" s="2" t="s">
         <v>42</v>
@@ -10318,152 +10223,152 @@
         <v>35</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>117</v>
+        <v>636</v>
       </c>
       <c r="X37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>443</v>
+        <v>637</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="AA37" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC37" s="2" t="s">
-        <v>444</v>
+        <v>638</v>
       </c>
       <c r="AD37" s="2" t="s">
-        <v>445</v>
+        <v>639</v>
       </c>
       <c r="AE37" s="2" t="s">
-        <v>446</v>
+        <v>640</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>447</v>
+        <v>641</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>51</v>
+        <v>642</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>448</v>
+        <v>643</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ37" s="2" t="s">
-        <v>54</v>
+        <v>644</v>
+      </c>
+      <c r="AJ37" s="7">
+        <v>0.3327</v>
       </c>
       <c r="AK37" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="AL37" s="2" t="s">
-        <v>450</v>
+        <v>645</v>
+      </c>
+      <c r="AL37" s="7">
+        <v>0.38300000000000001</v>
       </c>
       <c r="AM37" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="AN37" s="2" t="s">
-        <v>452</v>
+        <v>646</v>
+      </c>
+      <c r="AN37" s="7" t="s">
+        <v>647</v>
       </c>
       <c r="AO37" s="2" t="s">
-        <v>85</v>
+        <v>648</v>
       </c>
       <c r="AP37" s="1" t="s">
-        <v>198</v>
+        <v>592</v>
       </c>
       <c r="AQ37" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR37" s="2" t="s">
-        <v>453</v>
+        <v>649</v>
       </c>
       <c r="AS37" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT37" s="2" t="s">
-        <v>416</v>
+        <v>594</v>
       </c>
       <c r="AU37" s="2" t="s">
-        <v>454</v>
+        <v>65</v>
       </c>
       <c r="AV37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AW37" s="2" t="s">
-        <v>455</v>
+        <v>650</v>
       </c>
       <c r="AX37" s="2" t="s">
-        <v>67</v>
+        <v>651</v>
       </c>
       <c r="AY37" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ37" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA37" s="2" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="38" spans="1:53">
       <c r="A38" s="1" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>397</v>
+        <v>439</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>398</v>
+        <v>440</v>
       </c>
       <c r="E38" s="15">
-        <v>27.47</v>
+        <v>26.33</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="G38" s="15">
-        <v>32.229999999999997</v>
+        <v>28.67</v>
       </c>
       <c r="H38" s="15">
-        <v>22.94</v>
+        <v>21.01</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>399</v>
+        <v>441</v>
       </c>
       <c r="J38" s="14">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="K38" s="14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="L38" s="14">
         <f t="shared" si="0"/>
-        <v>29.9</v>
+        <v>26</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="N38" s="14">
-        <v>29.8</v>
+        <v>30</v>
       </c>
       <c r="O38" s="14">
-        <v>38.200000000000003</v>
+        <v>32</v>
       </c>
       <c r="P38" s="14">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>400</v>
+        <v>648</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>42</v>
@@ -10472,230 +10377,230 @@
         <v>35</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>401</v>
+        <v>117</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="Z38" s="2" t="s">
-        <v>403</v>
+        <v>46</v>
       </c>
       <c r="AA38" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>404</v>
+        <v>47</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>405</v>
+        <v>443</v>
       </c>
       <c r="AD38" s="2" t="s">
-        <v>406</v>
+        <v>444</v>
       </c>
       <c r="AE38" s="2" t="s">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>408</v>
+        <v>446</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>409</v>
+        <v>51</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>409</v>
+        <v>447</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>411</v>
+        <v>54</v>
       </c>
       <c r="AK38" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="AL38" s="7">
-        <v>0.46150000000000002</v>
+        <v>448</v>
+      </c>
+      <c r="AL38" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="AM38" s="2" t="s">
-        <v>413</v>
+        <v>450</v>
       </c>
       <c r="AN38" s="2" t="s">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="AO38" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AP38" s="1">
-        <v>7.0682870370370376E-4</v>
+      <c r="AP38" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="AQ38" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR38" s="2" t="s">
-        <v>415</v>
+        <v>452</v>
       </c>
       <c r="AS38" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT38" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AU38" s="2" t="s">
-        <v>65</v>
+        <v>453</v>
       </c>
       <c r="AV38" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AW38" s="2" t="s">
-        <v>417</v>
+        <v>454</v>
       </c>
       <c r="AX38" s="2" t="s">
-        <v>418</v>
+        <v>67</v>
       </c>
       <c r="AY38" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ38" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA38" s="2" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="39" spans="1:53">
       <c r="A39" s="1" t="s">
-        <v>792</v>
+        <v>535</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>791</v>
+        <v>395</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>796</v>
+        <v>396</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>844</v>
+        <v>397</v>
       </c>
       <c r="E39" s="15">
-        <v>27.11</v>
-      </c>
-      <c r="F39" s="4">
-        <v>26.83</v>
+        <v>27.47</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>1090</v>
       </c>
       <c r="G39" s="15">
-        <v>34.42</v>
+        <v>32.229999999999997</v>
       </c>
       <c r="H39" s="15">
-        <v>24.79</v>
+        <v>22.94</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>846</v>
+        <v>398</v>
       </c>
       <c r="J39" s="14">
+        <v>27.8</v>
+      </c>
+      <c r="K39" s="14">
         <v>32</v>
-      </c>
-      <c r="K39" s="14">
-        <v>33</v>
       </c>
       <c r="L39" s="14">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>29.9</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>846</v>
+        <v>1066</v>
       </c>
       <c r="N39" s="14">
-        <v>32</v>
+        <v>29.8</v>
       </c>
       <c r="O39" s="14">
-        <v>33</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="P39" s="14">
         <f t="shared" si="1"/>
-        <v>32.5</v>
+        <v>34</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="U39" s="10" t="s">
-        <v>85</v>
+        <v>399</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>701</v>
+        <v>35</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>845</v>
+        <v>400</v>
       </c>
       <c r="X39" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>847</v>
+        <v>401</v>
       </c>
       <c r="Z39" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA39" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB39" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AA39" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="AB39" s="2" t="s">
+      <c r="AC39" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="AC39" s="2" t="s">
-        <v>848</v>
-      </c>
       <c r="AD39" s="2" t="s">
-        <v>849</v>
+        <v>405</v>
       </c>
       <c r="AE39" s="2" t="s">
-        <v>690</v>
+        <v>406</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>691</v>
+        <v>407</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>929</v>
+        <v>408</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>693</v>
+        <v>408</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="AJ39" s="7">
-        <v>0.32100000000000001</v>
+        <v>409</v>
+      </c>
+      <c r="AJ39" s="2" t="s">
+        <v>410</v>
       </c>
       <c r="AK39" s="2" t="s">
-        <v>931</v>
+        <v>411</v>
       </c>
       <c r="AL39" s="7">
-        <v>0.51349999999999996</v>
-      </c>
-      <c r="AM39" s="9" t="s">
-        <v>932</v>
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="AM39" s="2" t="s">
+        <v>412</v>
       </c>
       <c r="AN39" s="2" t="s">
-        <v>933</v>
+        <v>413</v>
       </c>
       <c r="AO39" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="AP39" s="1" t="s">
-        <v>614</v>
+        <v>85</v>
+      </c>
+      <c r="AP39" s="1">
+        <v>7.0682870370370376E-4</v>
       </c>
       <c r="AQ39" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR39" s="2" t="s">
-        <v>924</v>
+        <v>414</v>
       </c>
       <c r="AS39" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT39" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AU39" s="2" t="s">
         <v>65</v>
@@ -10704,570 +10609,576 @@
         <v>65</v>
       </c>
       <c r="AW39" s="2" t="s">
-        <v>925</v>
+        <v>416</v>
       </c>
       <c r="AX39" s="2" t="s">
-        <v>926</v>
+        <v>417</v>
       </c>
       <c r="AY39" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ39" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="BA39" s="2" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="40" spans="1:53">
       <c r="A40" s="1" t="s">
-        <v>909</v>
+        <v>791</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>910</v>
+        <v>790</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>912</v>
+        <v>795</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>913</v>
+        <v>843</v>
+      </c>
+      <c r="E40" s="15">
+        <v>27.11</v>
+      </c>
+      <c r="F40" s="4">
+        <v>26.83</v>
+      </c>
+      <c r="G40" s="15">
+        <v>34.42</v>
+      </c>
+      <c r="H40" s="15">
+        <v>24.79</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>911</v>
+        <v>845</v>
       </c>
       <c r="J40" s="14">
         <v>32</v>
       </c>
       <c r="K40" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L40" s="14">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>1069</v>
+        <v>845</v>
       </c>
       <c r="N40" s="14">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O40" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="P40" s="14">
         <f t="shared" si="1"/>
-        <v>38.5</v>
+        <v>32.5</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="U40" s="10" t="s">
         <v>85</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>35</v>
+        <v>700</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>831</v>
+        <v>844</v>
       </c>
       <c r="X40" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>914</v>
+        <v>846</v>
       </c>
       <c r="Z40" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB40" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AA40" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="AB40" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="AC40" s="2" t="s">
-        <v>915</v>
+        <v>847</v>
       </c>
       <c r="AD40" s="2" t="s">
-        <v>915</v>
+        <v>848</v>
       </c>
       <c r="AE40" s="2" t="s">
-        <v>916</v>
+        <v>689</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>917</v>
+        <v>690</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>919</v>
+        <v>692</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="AJ40" s="7">
-        <v>0.32500000000000001</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="AK40" s="2" t="s">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="AL40" s="7">
-        <v>0.45660000000000001</v>
-      </c>
-      <c r="AM40" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="AN40" s="7" t="s">
-        <v>922</v>
+        <v>0.51349999999999996</v>
+      </c>
+      <c r="AM40" s="9"/>
+      <c r="AN40" s="2" t="s">
+        <v>931</v>
       </c>
       <c r="AO40" s="2" t="s">
-        <v>727</v>
+        <v>648</v>
       </c>
       <c r="AP40" s="1" t="s">
-        <v>923</v>
+        <v>613</v>
       </c>
       <c r="AQ40" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR40" s="2" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="AS40" s="2" t="s">
-        <v>928</v>
+        <v>63</v>
       </c>
       <c r="AT40" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
+      </c>
+      <c r="AU40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AW40" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="AX40" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="AY40" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AZ40" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
+      </c>
+      <c r="BA40" s="2" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="41" spans="1:53">
       <c r="A41" s="1" t="s">
-        <v>957</v>
+        <v>908</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>958</v>
+        <v>909</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>959</v>
+        <v>911</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>960</v>
-      </c>
-      <c r="E41" s="15">
-        <v>29.4</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G41" s="15">
-        <v>34.24</v>
-      </c>
-      <c r="H41" s="15">
-        <v>27.17</v>
+        <v>912</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>961</v>
+        <v>910</v>
       </c>
       <c r="J41" s="14">
+        <v>32</v>
+      </c>
+      <c r="K41" s="14">
         <v>35</v>
-      </c>
-      <c r="K41" s="14">
-        <v>36</v>
       </c>
       <c r="L41" s="14">
         <f t="shared" si="0"/>
-        <v>35.5</v>
+        <v>33.5</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>961</v>
+        <v>1067</v>
       </c>
       <c r="N41" s="14">
         <v>35</v>
       </c>
       <c r="O41" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P41" s="14">
         <f t="shared" si="1"/>
-        <v>35.5</v>
+        <v>38.5</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="U41" s="2" t="s">
-        <v>42</v>
+        <v>648</v>
+      </c>
+      <c r="U41" s="10" t="s">
+        <v>85</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>35</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>963</v>
+        <v>830</v>
       </c>
       <c r="X41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y41" s="2" t="s">
-        <v>964</v>
+        <v>913</v>
       </c>
       <c r="Z41" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="AA41" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB41" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AA41" s="2" t="s">
-        <v>768</v>
-      </c>
-      <c r="AB41" s="2" t="s">
-        <v>965</v>
-      </c>
       <c r="AC41" s="2" t="s">
-        <v>966</v>
+        <v>914</v>
       </c>
       <c r="AD41" s="2" t="s">
-        <v>967</v>
+        <v>914</v>
       </c>
       <c r="AE41" s="2" t="s">
-        <v>968</v>
+        <v>915</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>969</v>
+        <v>916</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>970</v>
+        <v>917</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>968</v>
+        <v>918</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>971</v>
+        <v>919</v>
       </c>
       <c r="AJ41" s="7">
-        <v>0.33900000000000002</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="AK41" s="2" t="s">
-        <v>972</v>
+        <v>920</v>
       </c>
       <c r="AL41" s="7">
-        <v>0.50270000000000004</v>
+        <v>0.45660000000000001</v>
       </c>
       <c r="AM41" s="2" t="s">
-        <v>553</v>
+        <v>860</v>
       </c>
       <c r="AN41" s="7" t="s">
-        <v>973</v>
+        <v>921</v>
       </c>
       <c r="AO41" s="2" t="s">
-        <v>974</v>
+        <v>726</v>
       </c>
       <c r="AP41" s="1" t="s">
-        <v>975</v>
+        <v>922</v>
       </c>
       <c r="AQ41" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR41" s="2" t="s">
-        <v>976</v>
+        <v>926</v>
       </c>
       <c r="AS41" s="2" t="s">
-        <v>977</v>
+        <v>927</v>
       </c>
       <c r="AT41" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="AW41" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="AX41" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="AY41" s="2" t="s">
-        <v>65</v>
+        <v>415</v>
       </c>
       <c r="AZ41" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="42" spans="1:53">
       <c r="A42" s="1" t="s">
-        <v>782</v>
+        <v>955</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>537</v>
+        <v>956</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>700</v>
+        <v>957</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>958</v>
       </c>
       <c r="E42" s="15">
-        <v>34.36</v>
-      </c>
-      <c r="F42" s="4">
-        <v>30.58</v>
+        <v>29.4</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>1091</v>
       </c>
       <c r="G42" s="15">
-        <v>37.549999999999997</v>
+        <v>34.24</v>
       </c>
       <c r="H42" s="15">
-        <v>26.75</v>
+        <v>27.17</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>635</v>
+        <v>959</v>
       </c>
       <c r="J42" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K42" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L42" s="14">
         <f t="shared" si="0"/>
         <v>35.5</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>635</v>
+        <v>959</v>
       </c>
       <c r="N42" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O42" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P42" s="14">
         <f t="shared" si="1"/>
         <v>35.5</v>
       </c>
-      <c r="Q42" s="14" t="s">
-        <v>1079</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>942</v>
+      <c r="T42" s="2" t="s">
+        <v>960</v>
       </c>
       <c r="U42" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>701</v>
+        <v>35</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>702</v>
+        <v>961</v>
       </c>
       <c r="X42" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y42" s="2" t="s">
-        <v>703</v>
+        <v>962</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA42" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>47</v>
+        <v>963</v>
       </c>
       <c r="AC42" s="2" t="s">
-        <v>640</v>
+        <v>964</v>
       </c>
       <c r="AD42" s="2" t="s">
-        <v>640</v>
+        <v>965</v>
       </c>
       <c r="AE42" s="2" t="s">
-        <v>641</v>
+        <v>966</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>642</v>
+        <v>967</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>704</v>
+        <v>968</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>705</v>
+        <v>966</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="AJ42" s="8">
-        <v>0.33</v>
+        <v>969</v>
+      </c>
+      <c r="AJ42" s="7">
+        <v>0.33900000000000002</v>
       </c>
       <c r="AK42" s="2" t="s">
-        <v>706</v>
+        <v>970</v>
       </c>
       <c r="AL42" s="7">
-        <v>0.57020000000000004</v>
+        <v>0.50270000000000004</v>
       </c>
       <c r="AM42" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="AN42" s="2" t="s">
-        <v>708</v>
+        <v>552</v>
+      </c>
+      <c r="AN42" s="7" t="s">
+        <v>971</v>
       </c>
       <c r="AO42" s="2" t="s">
-        <v>709</v>
+        <v>972</v>
       </c>
       <c r="AP42" s="1" t="s">
-        <v>710</v>
+        <v>973</v>
       </c>
       <c r="AQ42" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR42" s="2" t="s">
-        <v>711</v>
+        <v>974</v>
       </c>
       <c r="AS42" s="2" t="s">
-        <v>63</v>
+        <v>975</v>
       </c>
       <c r="AT42" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="AU42" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV42" s="2" t="s">
-        <v>65</v>
+        <v>615</v>
       </c>
       <c r="AW42" s="2" t="s">
-        <v>712</v>
+        <v>976</v>
       </c>
       <c r="AX42" s="2" t="s">
-        <v>713</v>
+        <v>977</v>
       </c>
       <c r="AY42" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ42" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="BA42" s="2" t="s">
-        <v>1024</v>
+        <v>984</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="16">
+    <row r="43" spans="1:53">
       <c r="A43" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>539</v>
+      <c r="B43" s="2" t="s">
+        <v>536</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16"/>
+        <v>699</v>
+      </c>
+      <c r="E43" s="15">
+        <v>34.36</v>
+      </c>
+      <c r="F43" s="4">
+        <v>30.58</v>
+      </c>
+      <c r="G43" s="15">
+        <v>37.549999999999997</v>
+      </c>
+      <c r="H43" s="15">
+        <v>26.75</v>
+      </c>
       <c r="I43" s="2" t="s">
-        <v>715</v>
+        <v>634</v>
       </c>
       <c r="J43" s="14">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K43" s="14">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L43" s="14">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>35.5</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>1070</v>
+        <v>634</v>
       </c>
       <c r="N43" s="14">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="O43" s="14">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="P43" s="14">
         <f t="shared" si="1"/>
-        <v>47.5</v>
-      </c>
-      <c r="T43" s="2" t="s">
-        <v>716</v>
+        <v>35.5</v>
+      </c>
+      <c r="Q43" s="14" t="s">
+        <v>1077</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>940</v>
       </c>
       <c r="U43" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V43" s="2" t="s">
-        <v>35</v>
+        <v>700</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="X43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y43" s="2" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="Z43" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AA43" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC43" s="2" t="s">
-        <v>719</v>
+        <v>639</v>
       </c>
       <c r="AD43" s="2" t="s">
-        <v>720</v>
+        <v>639</v>
       </c>
       <c r="AE43" s="2" t="s">
-        <v>721</v>
+        <v>640</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>722</v>
+        <v>641</v>
       </c>
       <c r="AG43" s="2" t="s">
-        <v>723</v>
+        <v>703</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>724</v>
+        <v>704</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="AJ43" s="7">
-        <v>0.33500000000000002</v>
+        <v>627</v>
+      </c>
+      <c r="AJ43" s="8">
+        <v>0.33</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>725</v>
+        <v>705</v>
       </c>
       <c r="AL43" s="7">
-        <v>0.49540000000000001</v>
+        <v>0.57020000000000004</v>
       </c>
       <c r="AM43" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="AN43" s="7" t="s">
-        <v>726</v>
+        <v>706</v>
+      </c>
+      <c r="AN43" s="2" t="s">
+        <v>707</v>
       </c>
       <c r="AO43" s="2" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="AP43" s="1" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="AQ43" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR43" s="2" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="AS43" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT43" s="2" t="s">
-        <v>683</v>
+        <v>615</v>
       </c>
       <c r="AU43" s="2" t="s">
         <v>65</v>
@@ -11276,74 +11187,66 @@
         <v>65</v>
       </c>
       <c r="AW43" s="2" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="AX43" s="2" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="AY43" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AZ43" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="BA43" s="2" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
-    <row r="44" spans="1:53">
+    <row r="44" spans="1:53" ht="16">
       <c r="A44" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>521</v>
+        <v>780</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>538</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>523</v>
-      </c>
-      <c r="E44" s="15">
-        <v>26.56</v>
-      </c>
-      <c r="F44" s="4">
-        <v>26.09</v>
-      </c>
-      <c r="G44" s="15">
-        <v>33.130000000000003</v>
-      </c>
-      <c r="H44" s="15">
-        <v>22.2</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>713</v>
+      </c>
+      <c r="E44" s="16"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="16"/>
       <c r="I44" s="2" t="s">
-        <v>524</v>
+        <v>714</v>
       </c>
       <c r="J44" s="14">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K44" s="14">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L44" s="14">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>524</v>
+        <v>1068</v>
       </c>
       <c r="N44" s="14">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="O44" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P44" s="14">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="Q44" s="14" t="s">
-        <v>1079</v>
+        <v>47.5</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>715</v>
       </c>
       <c r="U44" s="2" t="s">
         <v>42</v>
@@ -11352,76 +11255,76 @@
         <v>35</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>74</v>
+        <v>716</v>
       </c>
       <c r="X44" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y44" s="2" t="s">
-        <v>525</v>
+        <v>717</v>
       </c>
       <c r="Z44" s="2" t="s">
-        <v>76</v>
+        <v>402</v>
       </c>
       <c r="AA44" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB44" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC44" s="2" t="s">
-        <v>526</v>
+        <v>718</v>
       </c>
       <c r="AD44" s="2" t="s">
-        <v>527</v>
+        <v>719</v>
       </c>
       <c r="AE44" s="2" t="s">
-        <v>271</v>
+        <v>720</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>272</v>
+        <v>721</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>273</v>
+        <v>722</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>528</v>
+        <v>723</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AJ44" s="2" t="s">
-        <v>54</v>
+        <v>627</v>
+      </c>
+      <c r="AJ44" s="7">
+        <v>0.33500000000000002</v>
       </c>
       <c r="AK44" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="AL44" s="2" t="s">
-        <v>530</v>
+        <v>724</v>
+      </c>
+      <c r="AL44" s="7">
+        <v>0.49540000000000001</v>
       </c>
       <c r="AM44" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="AN44" s="2" t="s">
-        <v>532</v>
+        <v>552</v>
+      </c>
+      <c r="AN44" s="7" t="s">
+        <v>725</v>
       </c>
       <c r="AO44" s="2" t="s">
-        <v>85</v>
+        <v>726</v>
       </c>
       <c r="AP44" s="1" t="s">
-        <v>378</v>
+        <v>727</v>
       </c>
       <c r="AQ44" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR44" s="2" t="s">
-        <v>533</v>
+        <v>728</v>
       </c>
       <c r="AS44" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT44" s="2" t="s">
-        <v>416</v>
+        <v>682</v>
       </c>
       <c r="AU44" s="2" t="s">
         <v>65</v>
@@ -11430,81 +11333,80 @@
         <v>65</v>
       </c>
       <c r="AW44" s="2" t="s">
-        <v>534</v>
+        <v>729</v>
       </c>
       <c r="AX44" s="2" t="s">
-        <v>381</v>
+        <v>730</v>
       </c>
       <c r="AY44" s="2" t="s">
-        <v>535</v>
+        <v>65</v>
       </c>
       <c r="AZ44" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="BA44" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="19">
+    <row r="45" spans="1:53">
       <c r="A45" s="1" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>867</v>
+        <v>520</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>877</v>
+        <v>521</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>882</v>
-      </c>
-      <c r="E45" s="15"/>
+        <v>522</v>
+      </c>
+      <c r="E45" s="15">
+        <v>26.56</v>
+      </c>
       <c r="F45" s="4">
-        <v>24.13</v>
+        <v>26.09</v>
       </c>
       <c r="G45" s="15">
-        <v>29.39</v>
+        <v>33.130000000000003</v>
       </c>
       <c r="H45" s="15">
-        <v>22.11</v>
+        <v>22.2</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>883</v>
+        <v>523</v>
       </c>
       <c r="J45" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K45" s="14">
         <v>30</v>
       </c>
       <c r="L45" s="14">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>883</v>
+        <v>523</v>
       </c>
       <c r="N45" s="14">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O45" s="14">
         <v>30</v>
       </c>
       <c r="P45" s="14">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>1079</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>884</v>
+        <v>1077</v>
       </c>
       <c r="U45" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V45" s="2" t="s">
-        <v>701</v>
+        <v>35</v>
       </c>
       <c r="W45" s="2" t="s">
         <v>74</v>
@@ -11513,392 +11415,423 @@
         <v>44</v>
       </c>
       <c r="Y45" s="2" t="s">
-        <v>885</v>
+        <v>524</v>
       </c>
       <c r="Z45" s="2" t="s">
         <v>76</v>
       </c>
       <c r="AA45" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB45" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC45" s="2" t="s">
-        <v>886</v>
+        <v>525</v>
       </c>
       <c r="AD45" s="2" t="s">
-        <v>886</v>
+        <v>526</v>
       </c>
       <c r="AE45" s="2" t="s">
-        <v>887</v>
+        <v>271</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>888</v>
+        <v>272</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>889</v>
+        <v>273</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>887</v>
+        <v>527</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="AJ45" s="7">
-        <v>0.315</v>
+        <v>99</v>
+      </c>
+      <c r="AJ45" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="AK45" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="AL45" s="7">
-        <v>0.45700000000000002</v>
+        <v>528</v>
+      </c>
+      <c r="AL45" s="2" t="s">
+        <v>529</v>
       </c>
       <c r="AM45" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="AN45" s="7" t="s">
-        <v>893</v>
+        <v>530</v>
+      </c>
+      <c r="AN45" s="2" t="s">
+        <v>531</v>
       </c>
       <c r="AO45" s="2" t="s">
-        <v>613</v>
+        <v>85</v>
       </c>
       <c r="AP45" s="1" t="s">
-        <v>894</v>
+        <v>377</v>
       </c>
       <c r="AQ45" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR45" s="2" t="s">
-        <v>895</v>
+        <v>532</v>
       </c>
       <c r="AS45" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT45" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AW45" s="12" t="s">
-        <v>896</v>
+        <v>415</v>
+      </c>
+      <c r="AU45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AW45" s="2" t="s">
+        <v>533</v>
       </c>
       <c r="AX45" s="2" t="s">
-        <v>731</v>
+        <v>380</v>
       </c>
       <c r="AY45" s="2" t="s">
-        <v>897</v>
+        <v>534</v>
       </c>
       <c r="AZ45" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
+      </c>
+      <c r="BA45" s="2" t="s">
+        <v>1024</v>
       </c>
     </row>
-    <row r="46" spans="1:53">
+    <row r="46" spans="1:53" ht="19">
       <c r="A46" s="1" t="s">
-        <v>868</v>
+        <v>792</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>794</v>
+        <v>866</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>850</v>
-      </c>
-      <c r="E46" s="16">
-        <v>26.2</v>
-      </c>
-      <c r="F46" s="17">
-        <v>26.09</v>
-      </c>
-      <c r="G46" s="16">
-        <v>28.35</v>
-      </c>
-      <c r="H46" s="16">
-        <v>24.04</v>
+        <v>876</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="E46" s="15"/>
+      <c r="F46" s="4">
+        <v>24.13</v>
+      </c>
+      <c r="G46" s="15">
+        <v>29.39</v>
+      </c>
+      <c r="H46" s="15">
+        <v>22.11</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>851</v>
+        <v>882</v>
       </c>
       <c r="J46" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K46" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L46" s="14">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>851</v>
+        <v>882</v>
       </c>
       <c r="N46" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O46" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P46" s="14">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>1079</v>
-      </c>
-      <c r="R46" s="9" t="s">
-        <v>941</v>
+        <v>1077</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="U46" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>670</v>
+        <v>74</v>
       </c>
       <c r="X46" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>853</v>
+        <v>884</v>
       </c>
       <c r="Z46" s="2" t="s">
-        <v>403</v>
+        <v>76</v>
       </c>
       <c r="AA46" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC46" s="2" t="s">
-        <v>856</v>
+        <v>885</v>
       </c>
       <c r="AD46" s="2" t="s">
-        <v>857</v>
+        <v>885</v>
       </c>
       <c r="AE46" s="2" t="s">
-        <v>854</v>
+        <v>886</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>549</v>
+        <v>888</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="AJ46" s="8">
-        <v>0.32</v>
+        <v>889</v>
+      </c>
+      <c r="AJ46" s="7">
+        <v>0.315</v>
       </c>
       <c r="AK46" s="2" t="s">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="AL46" s="7">
-        <v>0.38140000000000002</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="AM46" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="AN46" s="2" t="s">
-        <v>862</v>
+        <v>891</v>
+      </c>
+      <c r="AN46" s="7" t="s">
+        <v>892</v>
       </c>
       <c r="AO46" s="2" t="s">
-        <v>863</v>
+        <v>612</v>
       </c>
       <c r="AP46" s="1" t="s">
-        <v>593</v>
+        <v>893</v>
       </c>
       <c r="AQ46" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR46" s="2" t="s">
-        <v>864</v>
+        <v>894</v>
       </c>
       <c r="AS46" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT46" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="AV46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AW46" s="2" t="s">
-        <v>865</v>
+        <v>415</v>
+      </c>
+      <c r="AW46" s="12" t="s">
+        <v>895</v>
       </c>
       <c r="AX46" s="2" t="s">
-        <v>681</v>
+        <v>730</v>
       </c>
       <c r="AY46" s="2" t="s">
-        <v>65</v>
+        <v>896</v>
       </c>
       <c r="AZ46" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="BA46" s="2" t="s">
-        <v>1027</v>
+        <v>986</v>
       </c>
     </row>
     <row r="47" spans="1:53">
       <c r="A47" s="1" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>869</v>
+        <v>793</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>878</v>
+        <v>796</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>901</v>
+        <v>849</v>
       </c>
       <c r="E47" s="16">
-        <v>22.77</v>
+        <v>26.2</v>
       </c>
       <c r="F47" s="17">
-        <v>22.81</v>
+        <v>26.09</v>
       </c>
       <c r="G47" s="16">
-        <v>30.56</v>
+        <v>28.35</v>
       </c>
       <c r="H47" s="16">
-        <v>11.84</v>
+        <v>24.04</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>1100</v>
+        <v>850</v>
       </c>
       <c r="J47" s="14">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K47" s="14">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="L47" s="14">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>1100</v>
+        <v>850</v>
       </c>
       <c r="N47" s="14">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="O47" s="14">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="P47" s="14">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R47" s="9" t="s">
-        <v>940</v>
+        <v>939</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>851</v>
       </c>
       <c r="U47" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>1040</v>
+        <v>669</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>1035</v>
+        <v>852</v>
       </c>
       <c r="Z47" s="2" t="s">
-        <v>1036</v>
+        <v>402</v>
       </c>
       <c r="AA47" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>904</v>
+        <v>855</v>
       </c>
       <c r="AD47" s="2" t="s">
-        <v>904</v>
+        <v>856</v>
       </c>
       <c r="AE47" s="2" t="s">
-        <v>641</v>
+        <v>853</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>642</v>
+        <v>854</v>
+      </c>
+      <c r="AG47" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="AH47" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="AI47" s="2" t="s">
+        <v>858</v>
       </c>
       <c r="AJ47" s="8">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="AK47" s="2" t="s">
-        <v>1038</v>
+        <v>859</v>
+      </c>
+      <c r="AL47" s="7">
+        <v>0.38140000000000002</v>
       </c>
       <c r="AM47" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="AN47" s="7" t="s">
-        <v>1039</v>
+        <v>860</v>
+      </c>
+      <c r="AN47" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="AO47" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="AP47" s="1" t="s">
+        <v>592</v>
       </c>
       <c r="AQ47" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR47" s="2" t="s">
-        <v>1041</v>
+        <v>863</v>
       </c>
       <c r="AS47" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT47" s="2" t="s">
-        <v>595</v>
+        <v>415</v>
+      </c>
+      <c r="AV47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AW47" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="AX47" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="AY47" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="AZ47" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="BA47" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="48" spans="1:53">
       <c r="A48" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="E48" s="16">
-        <v>22.67</v>
+        <v>22.77</v>
       </c>
       <c r="F48" s="17">
-        <v>22.7</v>
+        <v>22.81</v>
       </c>
       <c r="G48" s="16">
-        <v>28.54</v>
+        <v>30.56</v>
       </c>
       <c r="H48" s="16">
-        <v>12.94</v>
+        <v>11.84</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="J48" s="14">
         <v>15</v>
@@ -11911,7 +11844,7 @@
         <v>15</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="N48" s="14">
         <v>15</v>
@@ -11924,105 +11857,105 @@
         <v>15</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R48" s="9" t="s">
-        <v>939</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>1047</v>
+        <v>938</v>
       </c>
       <c r="U48" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="Z48" s="2" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AA48" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC48" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="AE48" s="2" t="s">
+        <v>640</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="AH48" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="AJ48" s="7">
-        <v>0.29899999999999999</v>
+        <v>641</v>
+      </c>
+      <c r="AJ48" s="8">
+        <v>0.15</v>
       </c>
       <c r="AK48" s="2" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="AM48" s="2" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="AN48" s="7" t="s">
-        <v>1046</v>
-      </c>
-      <c r="AO48" s="2" t="s">
-        <v>592</v>
+        <v>1037</v>
       </c>
       <c r="AQ48" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AR48" s="2" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="AS48" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT48" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AZ48" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
+      </c>
+      <c r="BA48" s="2" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="49" spans="1:53">
       <c r="A49" s="1" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="E49" s="16">
-        <v>22.41</v>
+        <v>22.67</v>
       </c>
       <c r="F49" s="17">
-        <v>22.48</v>
+        <v>22.7</v>
       </c>
       <c r="G49" s="16">
-        <v>27.8</v>
+        <v>28.54</v>
       </c>
       <c r="H49" s="16">
-        <v>13.62</v>
+        <v>12.94</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="J49" s="14">
         <v>15</v>
@@ -12035,7 +11968,7 @@
         <v>15</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="N49" s="14">
         <v>15</v>
@@ -12048,87 +11981,105 @@
         <v>15</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R49" s="9" t="s">
-        <v>938</v>
+        <v>937</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>1045</v>
       </c>
       <c r="U49" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V49" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>74</v>
+        <v>1040</v>
       </c>
       <c r="X49" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Y49" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AA49" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC49" s="2" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>899</v>
+        <v>897</v>
+      </c>
+      <c r="AH49" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AJ49" s="7">
+        <v>0.29899999999999999</v>
       </c>
       <c r="AK49" s="2" t="s">
-        <v>1038</v>
+        <v>1043</v>
+      </c>
+      <c r="AM49" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AN49" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AO49" s="2" t="s">
+        <v>591</v>
       </c>
       <c r="AQ49" s="2" t="s">
         <v>61</v>
       </c>
+      <c r="AR49" s="2" t="s">
+        <v>1046</v>
+      </c>
       <c r="AS49" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AT49" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AZ49" s="2" t="s">
-        <v>988</v>
-      </c>
-      <c r="BA49" s="2" t="s">
-        <v>1029</v>
+        <v>986</v>
       </c>
     </row>
     <row r="50" spans="1:53">
       <c r="A50" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="E50" s="16">
-        <v>22.58</v>
+        <v>22.41</v>
       </c>
       <c r="F50" s="17">
-        <v>22.58</v>
+        <v>22.48</v>
       </c>
       <c r="G50" s="16">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
       <c r="H50" s="16">
-        <v>14.83</v>
+        <v>13.62</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="J50" s="14">
         <v>15</v>
@@ -12141,7 +12092,7 @@
         <v>15</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="N50" s="14">
         <v>15</v>
@@ -12154,16 +12105,16 @@
         <v>15</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="R50" s="9" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="U50" s="2" t="s">
         <v>42</v>
       </c>
       <c r="V50" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>74</v>
@@ -12172,25 +12123,25 @@
         <v>44</v>
       </c>
       <c r="Y50" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="AA50" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AB50" s="2" t="s">
         <v>47</v>
       </c>
       <c r="AC50" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="AF50" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="AK50" s="2" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="AQ50" s="2" t="s">
         <v>61</v>
@@ -12199,87 +12150,193 @@
         <v>63</v>
       </c>
       <c r="AT50" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AZ50" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
+      </c>
+      <c r="BA50" s="2" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="51" spans="1:53">
+      <c r="A51" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>906</v>
+      </c>
+      <c r="E51" s="16">
+        <v>22.58</v>
+      </c>
+      <c r="F51" s="17">
+        <v>22.58</v>
+      </c>
+      <c r="G51" s="16">
+        <v>28.38</v>
+      </c>
+      <c r="H51" s="16">
+        <v>14.83</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="J51" s="14">
+        <v>15</v>
+      </c>
+      <c r="K51" s="14">
+        <v>15</v>
+      </c>
+      <c r="L51" s="14">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="N51" s="14">
+        <v>15</v>
+      </c>
+      <c r="O51" s="14">
+        <v>15</v>
+      </c>
+      <c r="P51" s="14">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Q51" s="14" t="s">
+        <v>1077</v>
+      </c>
+      <c r="R51" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="U51" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y51" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="Z51" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AA51" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="AB51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC51" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="AF51" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="AK51" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AQ51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AT51" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="AZ51" s="2" t="s">
+        <v>986</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AY44">
-    <sortCondition ref="A2:A44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AY45">
+    <sortCondition ref="A2:A45"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D27" r:id="rId1" xr:uid="{2586FB32-83C9-5143-BB4F-058E832A82A0}"/>
+    <hyperlink ref="D28" r:id="rId1" xr:uid="{2586FB32-83C9-5143-BB4F-058E832A82A0}"/>
     <hyperlink ref="D13" r:id="rId2" xr:uid="{3087E43A-F3CE-F048-8BC5-04F7F3819704}"/>
-    <hyperlink ref="D28" r:id="rId3" xr:uid="{6AF4FAC2-25E8-6649-8584-A8B7FBE1E12C}"/>
+    <hyperlink ref="D29" r:id="rId3" xr:uid="{6AF4FAC2-25E8-6649-8584-A8B7FBE1E12C}"/>
     <hyperlink ref="D8" r:id="rId4" xr:uid="{B7A01F15-9F78-E74F-9C2C-7C193F5DFA66}"/>
-    <hyperlink ref="D33" r:id="rId5" xr:uid="{A6A7777D-001D-3F4A-B294-A425F4327DBD}"/>
+    <hyperlink ref="D34" r:id="rId5" xr:uid="{A6A7777D-001D-3F4A-B294-A425F4327DBD}"/>
     <hyperlink ref="D20" r:id="rId6" xr:uid="{BA6B337B-529E-4748-A09D-B60E53C89698}"/>
     <hyperlink ref="D5" r:id="rId7" xr:uid="{0C52B2DD-F5F8-BC4D-8DC3-498C7B4F9507}"/>
     <hyperlink ref="D22" r:id="rId8" xr:uid="{45967181-1A6F-B244-BC8B-055BD4A62DDA}"/>
     <hyperlink ref="D11" r:id="rId9" xr:uid="{84287109-986F-F041-A592-89EB4754FA7C}"/>
-    <hyperlink ref="D37" r:id="rId10" xr:uid="{DF2175D6-71A9-1F40-9888-86F0CAE925C5}"/>
+    <hyperlink ref="D38" r:id="rId10" xr:uid="{DF2175D6-71A9-1F40-9888-86F0CAE925C5}"/>
     <hyperlink ref="D7" r:id="rId11" xr:uid="{5A8004AB-DA86-624F-A1F2-99000FF4DA4D}"/>
-    <hyperlink ref="D29" r:id="rId12" xr:uid="{291F978A-7A87-C148-8A37-04BE3AA210F0}"/>
-    <hyperlink ref="D30" r:id="rId13" xr:uid="{93C369C5-98A4-5443-BB4D-73F694BFD636}"/>
+    <hyperlink ref="D30" r:id="rId12" xr:uid="{291F978A-7A87-C148-8A37-04BE3AA210F0}"/>
+    <hyperlink ref="D31" r:id="rId13" xr:uid="{93C369C5-98A4-5443-BB4D-73F694BFD636}"/>
     <hyperlink ref="D3" r:id="rId14" xr:uid="{46A7479C-AC00-9C4C-8C39-8C74AC400E29}"/>
     <hyperlink ref="D14" r:id="rId15" xr:uid="{D13DF7E0-51EF-1F40-BB1A-D54222E58799}"/>
     <hyperlink ref="D4" r:id="rId16" xr:uid="{701D45D1-AE7B-064A-914A-8D279DAB28BC}"/>
     <hyperlink ref="D10" r:id="rId17" xr:uid="{79D560BB-9F4C-984C-9EDF-F77F2A3C575D}"/>
     <hyperlink ref="D18" r:id="rId18" xr:uid="{4CFF8BBA-796B-4643-AC66-6088096596A4}"/>
-    <hyperlink ref="D32" r:id="rId19" xr:uid="{EEFF5154-7C3B-BE42-8567-516A74F0AFAB}"/>
-    <hyperlink ref="D44" r:id="rId20" xr:uid="{68483CFF-7E4D-304F-A665-AA969647A78D}"/>
+    <hyperlink ref="D33" r:id="rId19" xr:uid="{EEFF5154-7C3B-BE42-8567-516A74F0AFAB}"/>
+    <hyperlink ref="D45" r:id="rId20" xr:uid="{68483CFF-7E4D-304F-A665-AA969647A78D}"/>
     <hyperlink ref="D17" r:id="rId21" xr:uid="{CC68842D-6E44-D541-B251-0A817FC7969B}"/>
     <hyperlink ref="D9" r:id="rId22" xr:uid="{35CB2CAD-A5DF-5C4F-8785-F6AC69FE7D5D}"/>
-    <hyperlink ref="D38" r:id="rId23" xr:uid="{832556FF-3A35-AE42-9D5A-01FAF6FE48C4}"/>
+    <hyperlink ref="D39" r:id="rId23" xr:uid="{832556FF-3A35-AE42-9D5A-01FAF6FE48C4}"/>
     <hyperlink ref="D2" r:id="rId24" xr:uid="{54568861-9615-0A45-A221-897BA104A2A8}"/>
     <hyperlink ref="D6" r:id="rId25" xr:uid="{AAC3965B-AFC6-8943-9568-CBEAF5CEE991}"/>
     <hyperlink ref="D16" r:id="rId26" xr:uid="{92835801-E3D7-6342-A65F-227FB99750A5}"/>
     <hyperlink ref="D24" r:id="rId27" xr:uid="{9FB278BD-A4AC-2447-A69A-C2953CBDA20A}"/>
-    <hyperlink ref="D36" r:id="rId28" xr:uid="{BECB3109-A83C-9D45-8DB6-05FB957668F1}"/>
-    <hyperlink ref="D35" r:id="rId29" xr:uid="{17D902E2-053F-CC42-A2AC-32B683131EBC}"/>
-    <hyperlink ref="D31" r:id="rId30" xr:uid="{8BA9AAE8-4EFB-A146-AD00-A72861F255C6}"/>
-    <hyperlink ref="D34" r:id="rId31" xr:uid="{3FE86DDB-0A0E-A94C-B6BA-89A958520378}"/>
-    <hyperlink ref="D42" r:id="rId32" xr:uid="{6BB9142A-9EBA-1441-B76F-B5C502E3E054}"/>
-    <hyperlink ref="D43" r:id="rId33" xr:uid="{36D90122-15CB-6445-A131-F3F427537159}"/>
+    <hyperlink ref="D37" r:id="rId28" xr:uid="{BECB3109-A83C-9D45-8DB6-05FB957668F1}"/>
+    <hyperlink ref="D36" r:id="rId29" xr:uid="{17D902E2-053F-CC42-A2AC-32B683131EBC}"/>
+    <hyperlink ref="D32" r:id="rId30" xr:uid="{8BA9AAE8-4EFB-A146-AD00-A72861F255C6}"/>
+    <hyperlink ref="D35" r:id="rId31" xr:uid="{3FE86DDB-0A0E-A94C-B6BA-89A958520378}"/>
+    <hyperlink ref="D43" r:id="rId32" xr:uid="{6BB9142A-9EBA-1441-B76F-B5C502E3E054}"/>
+    <hyperlink ref="D44" r:id="rId33" xr:uid="{36D90122-15CB-6445-A131-F3F427537159}"/>
     <hyperlink ref="D21" r:id="rId34" xr:uid="{FA4E2A9E-0C8C-1B4D-83FD-FA2DA91684B4}"/>
     <hyperlink ref="D19" r:id="rId35" xr:uid="{E18CF7F2-FDD1-374F-B631-23FC6170DB71}"/>
     <hyperlink ref="D26" r:id="rId36" xr:uid="{D8D42D71-0A53-6F46-B8BA-5FC8C940A579}"/>
     <hyperlink ref="D25" r:id="rId37" xr:uid="{4843720B-CC59-0342-A13F-09B09A71D45E}"/>
     <hyperlink ref="D15" r:id="rId38" xr:uid="{7CBAF161-7EC5-C248-A10A-44C219139D0B}"/>
-    <hyperlink ref="D39" r:id="rId39" xr:uid="{22DC5507-CC56-864E-8BC4-985EEC27213D}"/>
-    <hyperlink ref="D46" r:id="rId40" xr:uid="{5898C354-B224-A240-A9FF-9CBE55D3B711}"/>
-    <hyperlink ref="D45" r:id="rId41" xr:uid="{B26DC40D-168C-044B-BAB7-24C974CE81F4}"/>
-    <hyperlink ref="D47" r:id="rId42" xr:uid="{FA416C5F-52F6-FD4B-B17C-2122B959E022}"/>
-    <hyperlink ref="D48" r:id="rId43" xr:uid="{C5E74B53-4F4F-3545-8B13-C8835441B684}"/>
-    <hyperlink ref="D49" r:id="rId44" xr:uid="{A3A70E41-D9C4-D74F-BF46-406D278A338D}"/>
-    <hyperlink ref="D50" r:id="rId45" xr:uid="{70FDDF65-CF5C-204D-A285-F382553E7D5E}"/>
-    <hyperlink ref="D40" r:id="rId46" xr:uid="{013869AD-3839-9949-BD78-138181727368}"/>
-    <hyperlink ref="AM39" r:id="rId47" location=":~:text=%E6%A8%93%E5%B1%A4%E8%A6%8F%E5%8A%83%EF%BC%9A-,%E5%9C%B0%E4%B8%8A14%E5%B1%A4%EF%BC%8C%E5%9C%B0%E4%B8%8B4%E5%B1%A4,-%E8%BB%8A%E4%BD%8D%E8%A6%8F%E5%8A%83%EF%BC%9A" xr:uid="{1D7C1FF6-699C-3D42-9FD6-E803B0EB879E}"/>
-    <hyperlink ref="R50" r:id="rId48" xr:uid="{45E5744C-2297-5249-919F-E8100A7412C2}"/>
-    <hyperlink ref="R49" r:id="rId49" xr:uid="{2ABBD1D3-4997-E643-B81B-99C7652DBF8E}"/>
-    <hyperlink ref="R48" r:id="rId50" xr:uid="{A9611226-F1F2-8845-B4F2-E24216072372}"/>
-    <hyperlink ref="R47" r:id="rId51" xr:uid="{7EC0A553-B3B8-7F44-9C11-54ED356A5137}"/>
-    <hyperlink ref="R46" r:id="rId52" xr:uid="{5EFC57F9-D69B-CD4C-B170-34B84F99466D}"/>
-    <hyperlink ref="R32" r:id="rId53" xr:uid="{D5178C7D-72D8-1C45-A46F-C5BE87520D74}"/>
-    <hyperlink ref="R28" r:id="rId54" xr:uid="{C439EE12-B738-614D-9659-C664A5927CDF}"/>
-    <hyperlink ref="R27" r:id="rId55" xr:uid="{B5963B89-4E6B-BE4A-BFF9-C91A4C5DD556}"/>
-    <hyperlink ref="R24" r:id="rId56" xr:uid="{78663025-8F04-F842-9C43-15B19CD89A27}"/>
-    <hyperlink ref="R20" r:id="rId57" xr:uid="{F9795351-78C0-5647-B13A-6B9CA2A4852F}"/>
-    <hyperlink ref="R19" r:id="rId58" xr:uid="{E9E739D1-05BF-0143-94D3-A8770BAC0EC3}"/>
-    <hyperlink ref="R13" r:id="rId59" xr:uid="{E2EBE5B8-46EF-F444-83C1-DC75351B9475}"/>
-    <hyperlink ref="R12" r:id="rId60" xr:uid="{BCDE8407-65EE-BF42-90E3-D19E9AE73C6B}"/>
-    <hyperlink ref="R8" r:id="rId61" xr:uid="{72D8EA79-1383-EE44-AA01-F26EFCD2CD24}"/>
-    <hyperlink ref="R5" r:id="rId62" xr:uid="{F3D01D5C-AFFF-264E-A582-4DD0DDFC84C7}"/>
-    <hyperlink ref="R4" r:id="rId63" xr:uid="{84C54EA4-D033-AC43-947A-36013AC503E3}"/>
-    <hyperlink ref="D41" r:id="rId64" xr:uid="{5D605B83-C0B5-6247-8E1F-76A070BB09FC}"/>
-    <hyperlink ref="BA13" r:id="rId65" xr:uid="{CFD41646-E757-ED43-ABA1-CABF00E32E92}"/>
-    <hyperlink ref="BA17" r:id="rId66" xr:uid="{15356CC6-D40A-6B4A-8042-A37FA29279E1}"/>
-    <hyperlink ref="BA32" r:id="rId67" xr:uid="{B01C4786-26E9-AD46-B1BA-AEA2C6C8405B}"/>
-    <hyperlink ref="D23" r:id="rId68" xr:uid="{E4A9568D-65A4-3F46-84D7-82A6B7BB96B6}"/>
-    <hyperlink ref="BA22" r:id="rId69" xr:uid="{E5A55661-5BE7-C748-BA92-C63CC5BD349D}"/>
+    <hyperlink ref="D40" r:id="rId39" xr:uid="{22DC5507-CC56-864E-8BC4-985EEC27213D}"/>
+    <hyperlink ref="D47" r:id="rId40" xr:uid="{5898C354-B224-A240-A9FF-9CBE55D3B711}"/>
+    <hyperlink ref="D46" r:id="rId41" xr:uid="{B26DC40D-168C-044B-BAB7-24C974CE81F4}"/>
+    <hyperlink ref="D48" r:id="rId42" xr:uid="{FA416C5F-52F6-FD4B-B17C-2122B959E022}"/>
+    <hyperlink ref="D49" r:id="rId43" xr:uid="{C5E74B53-4F4F-3545-8B13-C8835441B684}"/>
+    <hyperlink ref="D50" r:id="rId44" xr:uid="{A3A70E41-D9C4-D74F-BF46-406D278A338D}"/>
+    <hyperlink ref="D51" r:id="rId45" xr:uid="{70FDDF65-CF5C-204D-A285-F382553E7D5E}"/>
+    <hyperlink ref="D41" r:id="rId46" xr:uid="{013869AD-3839-9949-BD78-138181727368}"/>
+    <hyperlink ref="R51" r:id="rId47" xr:uid="{45E5744C-2297-5249-919F-E8100A7412C2}"/>
+    <hyperlink ref="R50" r:id="rId48" xr:uid="{2ABBD1D3-4997-E643-B81B-99C7652DBF8E}"/>
+    <hyperlink ref="R49" r:id="rId49" xr:uid="{A9611226-F1F2-8845-B4F2-E24216072372}"/>
+    <hyperlink ref="R48" r:id="rId50" xr:uid="{7EC0A553-B3B8-7F44-9C11-54ED356A5137}"/>
+    <hyperlink ref="R47" r:id="rId51" xr:uid="{5EFC57F9-D69B-CD4C-B170-34B84F99466D}"/>
+    <hyperlink ref="R33" r:id="rId52" xr:uid="{D5178C7D-72D8-1C45-A46F-C5BE87520D74}"/>
+    <hyperlink ref="R29" r:id="rId53" xr:uid="{C439EE12-B738-614D-9659-C664A5927CDF}"/>
+    <hyperlink ref="R28" r:id="rId54" xr:uid="{B5963B89-4E6B-BE4A-BFF9-C91A4C5DD556}"/>
+    <hyperlink ref="R24" r:id="rId55" xr:uid="{78663025-8F04-F842-9C43-15B19CD89A27}"/>
+    <hyperlink ref="R20" r:id="rId56" xr:uid="{F9795351-78C0-5647-B13A-6B9CA2A4852F}"/>
+    <hyperlink ref="R19" r:id="rId57" xr:uid="{E9E739D1-05BF-0143-94D3-A8770BAC0EC3}"/>
+    <hyperlink ref="R13" r:id="rId58" xr:uid="{E2EBE5B8-46EF-F444-83C1-DC75351B9475}"/>
+    <hyperlink ref="R12" r:id="rId59" xr:uid="{BCDE8407-65EE-BF42-90E3-D19E9AE73C6B}"/>
+    <hyperlink ref="R8" r:id="rId60" xr:uid="{72D8EA79-1383-EE44-AA01-F26EFCD2CD24}"/>
+    <hyperlink ref="R5" r:id="rId61" xr:uid="{F3D01D5C-AFFF-264E-A582-4DD0DDFC84C7}"/>
+    <hyperlink ref="R4" r:id="rId62" xr:uid="{84C54EA4-D033-AC43-947A-36013AC503E3}"/>
+    <hyperlink ref="D42" r:id="rId63" xr:uid="{5D605B83-C0B5-6247-8E1F-76A070BB09FC}"/>
+    <hyperlink ref="BA13" r:id="rId64" xr:uid="{CFD41646-E757-ED43-ABA1-CABF00E32E92}"/>
+    <hyperlink ref="BA17" r:id="rId65" xr:uid="{15356CC6-D40A-6B4A-8042-A37FA29279E1}"/>
+    <hyperlink ref="BA33" r:id="rId66" xr:uid="{B01C4786-26E9-AD46-B1BA-AEA2C6C8405B}"/>
+    <hyperlink ref="D23" r:id="rId67" xr:uid="{E4A9568D-65A4-3F46-84D7-82A6B7BB96B6}"/>
+    <hyperlink ref="BA22" r:id="rId68" xr:uid="{E5A55661-5BE7-C748-BA92-C63CC5BD349D}"/>
+    <hyperlink ref="D27" r:id="rId69" xr:uid="{1AF6D948-8F97-FF4A-9972-F11D72F7EA81}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-1101-House.xlsx
+++ b/db/A7XLK-1101-House.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC110A17-7C8D-804D-A0F0-8F0556A56051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A4FB02-4F9E-8247-AFB8-71408BF18888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17020" yWindow="-14100" windowWidth="36360" windowHeight="13780" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
+    <workbookView xWindow="18520" yWindow="2400" windowWidth="27980" windowHeight="17500" xr2:uid="{82CCD04F-99AF-E049-A4F3-18018514BF0A}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -4678,7 +4678,7 @@
   <dimension ref="A1:BA51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="12.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.1640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="28.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="60.33203125" style="2" customWidth="1"/>
